--- a/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/GameData.xlsx
+++ b/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/GameData.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13515" tabRatio="500" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
     <sheet name="TrackingConstants" sheetId="2" r:id="rId2"/>
     <sheet name="IDs" sheetId="3" r:id="rId3"/>
-    <sheet name="Characters" sheetId="4" r:id="rId4"/>
-    <sheet name="Enemies" sheetId="5" r:id="rId5"/>
-    <sheet name="EnemyAttacks" sheetId="6" r:id="rId6"/>
-    <sheet name="Mods" sheetId="7" r:id="rId7"/>
-    <sheet name="Equipments" sheetId="8" r:id="rId8"/>
-    <sheet name="RescueRewards" sheetId="9" r:id="rId9"/>
-    <sheet name="PlayerLevels" sheetId="10" r:id="rId10"/>
+    <sheet name="Configuration" sheetId="11" r:id="rId4"/>
+    <sheet name="Characters" sheetId="4" r:id="rId5"/>
+    <sheet name="Enemies" sheetId="5" r:id="rId6"/>
+    <sheet name="EnemyAttacks" sheetId="6" r:id="rId7"/>
+    <sheet name="Mods" sheetId="7" r:id="rId8"/>
+    <sheet name="Equipments" sheetId="8" r:id="rId9"/>
+    <sheet name="RescueRewards" sheetId="9" r:id="rId10"/>
+    <sheet name="PlayerLevels" sheetId="10" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Enemies!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Enemies!$A$1:$O$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -842,7 +843,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="996">
   <si>
     <t>Name</t>
   </si>
@@ -2452,6 +2453,105 @@
     <t>MOD_EVOL_ATK_RANGE_INC</t>
   </si>
   <si>
+    <t>Sub Class</t>
+  </si>
+  <si>
+    <t>Field Name</t>
+  </si>
+  <si>
+    <t>economy</t>
+  </si>
+  <si>
+    <t>startingCoins</t>
+  </si>
+  <si>
+    <t>startingGems</t>
+  </si>
+  <si>
+    <t>dailyRewardBase</t>
+  </si>
+  <si>
+    <t>reviveCostCoins</t>
+  </si>
+  <si>
+    <t>energyCap</t>
+  </si>
+  <si>
+    <t>energyRechargeSec</t>
+  </si>
+  <si>
+    <t>gameBalance</t>
+  </si>
+  <si>
+    <t>basePlayerHp</t>
+  </si>
+  <si>
+    <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>respawnDelaySec</t>
+  </si>
+  <si>
+    <t>levelCap</t>
+  </si>
+  <si>
+    <t>difficultyMultiplier[]</t>
+  </si>
+  <si>
+    <t>1.0|1.2|1.5|2.0</t>
+  </si>
+  <si>
+    <t>dropRates[]</t>
+  </si>
+  <si>
+    <t>0.7|0.25|0.05</t>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>maintenanceMode</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>minAppVersion</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
+    <t>enableShop</t>
+  </si>
+  <si>
+    <t>enablePvP</t>
+  </si>
+  <si>
+    <t>interstitialIntervalSec</t>
+  </si>
+  <si>
+    <t>rewardedAdPlacement</t>
+  </si>
+  <si>
+    <t>Placement_DoubleReward</t>
+  </si>
+  <si>
+    <t>position3</t>
+  </si>
+  <si>
+    <t>vector3</t>
+  </si>
+  <si>
+    <t>1|2|3</t>
+  </si>
+  <si>
+    <t>position2</t>
+  </si>
+  <si>
+    <t>1.0|2.0</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -2462,9 +2562,6 @@
   </si>
   <si>
     <t>atk</t>
-  </si>
-  <si>
-    <t>moveSpeed</t>
   </si>
   <si>
     <t>dodgeChance</t>
@@ -3823,13 +3920,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3997,18 +4094,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="55">
+  <fills count="56">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4121,6 +4218,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE5D6"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -4562,19 +4665,19 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4583,7 +4686,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4607,16 +4710,16 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -4625,92 +4728,92 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -4729,9 +4832,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="50" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="49" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="51" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="51" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="49" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4855,46 +4958,51 @@
     <xf numFmtId="2" fontId="11" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="49" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="49" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="51" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="51" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" xfId="51" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="51" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4903,12 +5011,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -5300,7 +5408,7 @@
     <col min="14" max="14" width="7.85714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:14">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -5311,7 +5419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:14">
       <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
@@ -5322,7 +5430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:14">
       <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
@@ -5333,7 +5441,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:14">
       <c r="A4" s="24" t="s">
         <v>7</v>
       </c>
@@ -5344,7 +5452,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:14">
       <c r="A5" s="24" t="s">
         <v>8</v>
       </c>
@@ -5355,7 +5463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:14">
       <c r="A6" s="24" t="s">
         <v>9</v>
       </c>
@@ -5376,11 +5484,11 @@
       <c r="C7" s="24">
         <v>16</v>
       </c>
-      <c r="L7" s="148" t="s">
+      <c r="L7" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="148"/>
-      <c r="N7" s="148"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="24" t="s">
@@ -5392,9 +5500,9 @@
       <c r="C8" s="24">
         <v>2</v>
       </c>
-      <c r="L8" s="148"/>
-      <c r="M8" s="148"/>
-      <c r="N8" s="148"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="24" t="s">
@@ -5556,7 +5664,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:16">
       <c r="A17" s="24" t="s">
         <v>43</v>
       </c>
@@ -5567,423 +5675,423 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="11:16">
-      <c r="K18" s="149"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="149"/>
-      <c r="N18" s="149"/>
-      <c r="O18" s="149"/>
-      <c r="P18" s="149"/>
+    <row r="18" spans="1:16">
+      <c r="K18" s="148"/>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="148"/>
+      <c r="O18" s="148"/>
+      <c r="P18" s="148"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="144" t="s">
+      <c r="A19" s="149" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="144" t="s">
+      <c r="B19" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="144">
+      <c r="C19" s="149">
         <v>100</v>
       </c>
-      <c r="K19" s="149"/>
-      <c r="L19" s="149"/>
-      <c r="M19" s="149"/>
-      <c r="N19" s="149"/>
-      <c r="O19" s="149"/>
-      <c r="P19" s="149"/>
+      <c r="K19" s="148"/>
+      <c r="L19" s="148"/>
+      <c r="M19" s="148"/>
+      <c r="N19" s="148"/>
+      <c r="O19" s="148"/>
+      <c r="P19" s="148"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="144">
+      <c r="C20" s="149">
         <v>100</v>
       </c>
-      <c r="K20" s="149"/>
-      <c r="L20" s="149"/>
-      <c r="M20" s="149"/>
-      <c r="N20" s="149"/>
-      <c r="O20" s="149"/>
-      <c r="P20" s="149"/>
+      <c r="K20" s="148"/>
+      <c r="L20" s="148"/>
+      <c r="M20" s="148"/>
+      <c r="N20" s="148"/>
+      <c r="O20" s="148"/>
+      <c r="P20" s="148"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="144" t="s">
+      <c r="A21" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="144" t="s">
+      <c r="B21" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="149"/>
+      <c r="K21" s="148"/>
       <c r="L21" s="150"/>
       <c r="M21" s="150"/>
       <c r="N21" s="150"/>
-      <c r="O21" s="149"/>
-      <c r="P21" s="149"/>
+      <c r="O21" s="148"/>
+      <c r="P21" s="148"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="144" t="s">
+      <c r="A22" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="144" t="s">
+      <c r="B22" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="144">
+      <c r="C22" s="149">
         <v>5</v>
       </c>
-      <c r="K22" s="149"/>
+      <c r="K22" s="148"/>
       <c r="L22" s="150"/>
       <c r="M22" s="150"/>
       <c r="N22" s="150"/>
-      <c r="O22" s="149"/>
-      <c r="P22" s="149"/>
+      <c r="O22" s="148"/>
+      <c r="P22" s="148"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="144" t="s">
+      <c r="A23" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="144" t="s">
+      <c r="B23" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="144">
+      <c r="C23" s="149">
         <v>10</v>
       </c>
-      <c r="K23" s="149"/>
+      <c r="K23" s="148"/>
       <c r="L23" s="150"/>
       <c r="M23" s="150"/>
       <c r="N23" s="150"/>
-      <c r="O23" s="149"/>
-      <c r="P23" s="149"/>
+      <c r="O23" s="148"/>
+      <c r="P23" s="148"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="144" t="s">
+      <c r="B24" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="144">
+      <c r="C24" s="149">
         <v>5</v>
       </c>
-      <c r="K24" s="149"/>
+      <c r="K24" s="148"/>
       <c r="L24" s="150"/>
       <c r="M24" s="150"/>
       <c r="N24" s="150"/>
-      <c r="O24" s="149"/>
-      <c r="P24" s="149"/>
+      <c r="O24" s="148"/>
+      <c r="P24" s="148"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="145" t="s">
+      <c r="A25" s="151" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="145" t="s">
+      <c r="B25" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="145">
+      <c r="C25" s="151">
         <v>2</v>
       </c>
-      <c r="K25" s="149"/>
+      <c r="K25" s="148"/>
       <c r="L25" s="150"/>
       <c r="M25" s="150"/>
       <c r="N25" s="150"/>
-      <c r="O25" s="149"/>
-      <c r="P25" s="149"/>
+      <c r="O25" s="148"/>
+      <c r="P25" s="148"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="145" t="s">
+      <c r="B26" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="145">
+      <c r="C26" s="151">
         <v>2</v>
       </c>
-      <c r="K26" s="149"/>
+      <c r="K26" s="148"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
-      <c r="O26" s="149"/>
-      <c r="P26" s="149"/>
+      <c r="O26" s="148"/>
+      <c r="P26" s="148"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="145" t="s">
+      <c r="A27" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="145">
+      <c r="C27" s="151">
         <v>2</v>
       </c>
-      <c r="K27" s="149"/>
+      <c r="K27" s="148"/>
       <c r="L27" s="150"/>
       <c r="M27" s="150"/>
       <c r="N27" s="150"/>
-      <c r="O27" s="149"/>
-      <c r="P27" s="149"/>
+      <c r="O27" s="148"/>
+      <c r="P27" s="148"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="145" t="s">
+      <c r="A28" s="151" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="145" t="s">
+      <c r="B28" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="145">
+      <c r="C28" s="151">
         <v>2</v>
       </c>
-      <c r="K28" s="149"/>
+      <c r="K28" s="148"/>
       <c r="L28" s="150"/>
       <c r="M28" s="150"/>
       <c r="N28" s="150"/>
-      <c r="O28" s="149"/>
-      <c r="P28" s="149"/>
+      <c r="O28" s="148"/>
+      <c r="P28" s="148"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="145" t="s">
+      <c r="A29" s="151" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="145" t="s">
+      <c r="B29" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="145">
+      <c r="C29" s="151">
         <v>3</v>
       </c>
-      <c r="K29" s="149"/>
+      <c r="K29" s="148"/>
       <c r="L29" s="150"/>
       <c r="M29" s="150"/>
       <c r="N29" s="150"/>
-      <c r="O29" s="149"/>
-      <c r="P29" s="149"/>
-    </row>
-    <row r="30" spans="11:16">
-      <c r="K30" s="149"/>
+      <c r="O29" s="148"/>
+      <c r="P29" s="148"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="K30" s="148"/>
       <c r="L30" s="150"/>
       <c r="M30" s="150"/>
       <c r="N30" s="150"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="149"/>
+      <c r="O30" s="148"/>
+      <c r="P30" s="148"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="145" t="s">
+      <c r="B31" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="K31" s="149"/>
+      <c r="K31" s="148"/>
       <c r="L31" s="150"/>
       <c r="M31" s="150"/>
       <c r="N31" s="150"/>
-      <c r="O31" s="149"/>
-      <c r="P31" s="149"/>
+      <c r="O31" s="148"/>
+      <c r="P31" s="148"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="145" t="s">
+      <c r="B32" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="149" t="s">
         <v>59</v>
       </c>
-      <c r="K32" s="149"/>
+      <c r="K32" s="148"/>
       <c r="L32" s="150"/>
       <c r="M32" s="150"/>
       <c r="N32" s="150"/>
-      <c r="O32" s="149"/>
-      <c r="P32" s="149"/>
+      <c r="O32" s="148"/>
+      <c r="P32" s="148"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="145" t="s">
+      <c r="B33" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="144" t="s">
+      <c r="C33" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="K33" s="149"/>
+      <c r="K33" s="148"/>
       <c r="L33" s="150"/>
       <c r="M33" s="150"/>
       <c r="N33" s="150"/>
-      <c r="O33" s="149"/>
-      <c r="P33" s="149"/>
+      <c r="O33" s="148"/>
+      <c r="P33" s="148"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="144" t="s">
+      <c r="A34" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="K34" s="149"/>
+      <c r="K34" s="148"/>
       <c r="L34" s="150"/>
       <c r="M34" s="150"/>
       <c r="N34" s="150"/>
-      <c r="O34" s="149"/>
-      <c r="P34" s="149"/>
+      <c r="O34" s="148"/>
+      <c r="P34" s="148"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="144" t="s">
+      <c r="A35" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="145" t="s">
+      <c r="B35" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="144" t="s">
+      <c r="C35" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="K35" s="151"/>
-      <c r="L35" s="151"/>
-      <c r="M35" s="151"/>
-      <c r="N35" s="151"/>
-      <c r="O35" s="151"/>
-      <c r="P35" s="151"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="144" t="s">
+      <c r="K35" s="152"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="152"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="145" t="s">
+      <c r="B36" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="149" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="144" t="s">
+    <row r="37" spans="1:16">
+      <c r="A37" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="145" t="s">
+      <c r="B37" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="149" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="144" t="s">
+    <row r="38" spans="1:16">
+      <c r="A38" s="149" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="149" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="144" t="s">
+    <row r="39" spans="1:16">
+      <c r="A39" s="149" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="145" t="s">
+      <c r="B39" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="149" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="144" t="s">
+    <row r="40" spans="1:16">
+      <c r="A40" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="145" t="s">
+      <c r="B40" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="149" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="144" t="s">
+    <row r="41" spans="1:16">
+      <c r="A41" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="145" t="s">
+      <c r="B41" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="149" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="144" t="s">
+    <row r="42" spans="1:16">
+      <c r="A42" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="145" t="s">
+      <c r="B42" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="149" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="144" t="s">
+    <row r="43" spans="1:16">
+      <c r="A43" s="149" t="s">
         <v>80</v>
       </c>
-      <c r="B43" s="145" t="s">
+      <c r="B43" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="144" t="s">
+      <c r="C43" s="149" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="144" t="s">
+    <row r="44" spans="1:16">
+      <c r="A44" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="144" t="s">
+      <c r="C44" s="149" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" ht="19.5" spans="1:3">
-      <c r="A45" s="144" t="s">
+    <row r="45" ht="16.5" spans="1:16">
+      <c r="A45" s="149" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="145" t="s">
+      <c r="B45" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="146" t="s">
+      <c r="C45" s="153" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="144" t="s">
+    <row r="46" spans="1:16">
+      <c r="A46" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="145" t="s">
+      <c r="B46" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="149" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="147" t="s">
+    <row r="47" spans="1:16">
+      <c r="A47" s="154" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="147" t="s">
+      <c r="B47" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="147" t="s">
+      <c r="C47" s="154" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5998,6 +6106,285 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="22.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="26.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="12.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="4.57142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C1" t="s">
+        <v>897</v>
+      </c>
+      <c r="D1" t="s">
+        <v>898</v>
+      </c>
+      <c r="E1" t="s">
+        <v>899</v>
+      </c>
+      <c r="F1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <f t="shared" ref="F2:F12" si="0">E2/$G$2*100</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>SUM(E2:E12)</f>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9">
+        <v>4</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>120</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>20.7612456747405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="0"/>
+        <v>10.3806228373702</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="9">
+        <v>8</v>
+      </c>
+      <c r="E7" s="9">
+        <v>30</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="0"/>
+        <v>5.19031141868512</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <f>E10*5</f>
+        <v>200</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>34.6020761245675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <f>E8/2</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>17.3010380622837</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <f>E12*5</f>
+        <v>40</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>6.9204152249135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <f>E9/5</f>
+        <v>20</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="0"/>
+        <v>3.46020761245675</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11">
+        <v>8</v>
+      </c>
+      <c r="F12" s="12">
+        <f t="shared" si="0"/>
+        <v>1.3840830449827</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D71"/>
@@ -6014,16 +6401,16 @@
         <v>222</v>
       </c>
       <c r="B1" t="s">
-        <v>869</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
       <c r="D1" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:1">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -6033,13 +6420,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>873</v>
+        <v>905</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -6047,13 +6434,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>875</v>
+        <v>907</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -6061,13 +6448,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -6075,13 +6462,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -6089,13 +6476,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -6103,13 +6490,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>879</v>
+        <v>911</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
@@ -6117,13 +6504,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>880</v>
+        <v>912</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -6131,13 +6518,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>881</v>
+        <v>913</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
@@ -6145,13 +6532,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>883</v>
+        <v>915</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:4">
@@ -6159,13 +6546,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>885</v>
+        <v>917</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:4">
@@ -6173,13 +6560,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>887</v>
+        <v>919</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:4">
@@ -6187,13 +6574,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>888</v>
+        <v>920</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:4">
@@ -6201,13 +6588,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>889</v>
+        <v>921</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:4">
@@ -6215,13 +6602,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>890</v>
+        <v>922</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>891</v>
+        <v>923</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:4">
@@ -6229,13 +6616,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:4">
@@ -6243,13 +6630,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>893</v>
+        <v>925</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:4">
@@ -6257,13 +6644,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>894</v>
+        <v>926</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:4">
@@ -6271,13 +6658,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:4">
@@ -6285,13 +6672,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>898</v>
+        <v>930</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -6299,13 +6686,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>899</v>
+        <v>931</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
@@ -6313,13 +6700,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>901</v>
+        <v>933</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -6327,13 +6714,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -6341,13 +6728,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>903</v>
+        <v>935</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -6355,13 +6742,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -6369,13 +6756,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>906</v>
+        <v>938</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -6383,13 +6770,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -6397,13 +6784,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>908</v>
+        <v>940</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -6411,13 +6798,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -6425,13 +6812,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:4">
@@ -6439,13 +6826,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" spans="1:4">
@@ -6453,13 +6840,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:4">
@@ -6467,13 +6854,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:4">
@@ -6481,13 +6868,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" spans="1:4">
@@ -6495,13 +6882,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" spans="1:4">
@@ -6509,13 +6896,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:4">
@@ -6523,13 +6910,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" spans="1:4">
@@ -6537,13 +6924,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" spans="1:4">
@@ -6551,13 +6938,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>922</v>
+        <v>954</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:4">
@@ -6565,13 +6952,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:4">
@@ -6579,13 +6966,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:4">
@@ -6593,13 +6980,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:4">
@@ -6607,13 +6994,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:4">
@@ -6621,13 +7008,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:4">
@@ -6635,13 +7022,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:4">
@@ -6649,13 +7036,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>932</v>
+        <v>964</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:4">
@@ -6663,13 +7050,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:4">
@@ -6677,13 +7064,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>934</v>
+        <v>966</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:4">
@@ -6691,13 +7078,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:4">
@@ -6705,13 +7092,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:4">
@@ -6719,13 +7106,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>938</v>
+        <v>970</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" spans="1:4">
@@ -6733,13 +7120,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>940</v>
+        <v>972</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:4">
@@ -6747,13 +7134,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" spans="1:4">
@@ -6761,13 +7148,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" spans="1:4">
@@ -6775,13 +7162,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>943</v>
+        <v>975</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>944</v>
+        <v>976</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" spans="1:4">
@@ -6789,13 +7176,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="58" s="2" customFormat="1" spans="1:4">
@@ -6803,13 +7190,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>946</v>
+        <v>978</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" spans="1:4">
@@ -6817,13 +7204,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" spans="1:4">
@@ -6831,13 +7218,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" spans="1:4">
@@ -6845,13 +7232,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>950</v>
+        <v>982</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:4">
@@ -6859,13 +7246,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:4">
@@ -6873,13 +7260,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>953</v>
+        <v>985</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:4">
@@ -6887,13 +7274,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>954</v>
+        <v>986</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:4">
@@ -6901,13 +7288,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>955</v>
+        <v>987</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:4">
@@ -6915,13 +7302,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>957</v>
+        <v>989</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:4">
@@ -6929,13 +7316,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>958</v>
+        <v>990</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:4">
@@ -6943,13 +7330,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:4">
@@ -6957,13 +7344,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>960</v>
+        <v>992</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:4">
@@ -6971,13 +7358,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>961</v>
+        <v>993</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:4">
@@ -6985,13 +7372,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>962</v>
+        <v>994</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>963</v>
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -7014,7 +7401,7 @@
     <col min="5" max="5" width="16.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7026,640 +7413,640 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="136" t="s">
+      <c r="A2" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="136" t="s">
+      <c r="C2" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="136" t="s">
+      <c r="D2" s="139" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="139" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="136" t="s">
+      <c r="B3" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="136" t="s">
+      <c r="C3" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="136" t="s">
+      <c r="D3" s="139" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="139" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="139" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="136" t="s">
+      <c r="D4" s="139" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="139" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="136" t="s">
+      <c r="D5" s="139" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="136" t="s">
+      <c r="A6" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="136" t="s">
+      <c r="C6" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="136" t="s">
+      <c r="D6" s="139" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="139" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="136" t="s">
+      <c r="B7" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="136" t="s">
+      <c r="C7" s="139" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="136" t="s">
+      <c r="D7" s="139" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="136" t="s">
+      <c r="B8" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="136" t="s">
+      <c r="C8" s="139" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="139" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="136" t="s">
+      <c r="A9" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="136" t="s">
+      <c r="B9" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="136" t="s">
+      <c r="C9" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="136" t="s">
+      <c r="D9" s="139" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="136" t="s">
+      <c r="A10" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="136" t="s">
+      <c r="B10" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="136" t="s">
+      <c r="C10" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="136" t="s">
+      <c r="D10" s="139" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="136" t="s">
+      <c r="C11" s="139" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="136"/>
+      <c r="D11" s="139"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="136" t="s">
+      <c r="A12" s="139" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="136" t="s">
+      <c r="B12" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="136" t="s">
+      <c r="C12" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="136" t="s">
+      <c r="D12" s="139" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="136" t="s">
+      <c r="A13" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="136" t="s">
+      <c r="B13" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="136" t="s">
+      <c r="C13" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="136" t="s">
+      <c r="D13" s="139" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="136" t="s">
+      <c r="A14" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="136" t="s">
+      <c r="C14" s="139" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="136"/>
+      <c r="D14" s="139"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="136" t="s">
+      <c r="A15" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="136" t="s">
+      <c r="C15" s="139" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="139" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="136" t="s">
+      <c r="A16" s="139" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="136" t="s">
+      <c r="B16" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="136" t="s">
+      <c r="C16" s="139" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="136" t="s">
+      <c r="D16" s="139" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="136" t="s">
+      <c r="A17" s="139" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="136" t="s">
+      <c r="B17" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="136" t="s">
+      <c r="C17" s="139" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="136" t="s">
+      <c r="D17" s="139" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="136" t="s">
+      <c r="A18" s="139" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="136" t="s">
+      <c r="B18" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="136" t="s">
+      <c r="C18" s="139" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="136" t="s">
+      <c r="D18" s="139" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="136" t="s">
+      <c r="A19" s="139" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="136" t="s">
+      <c r="B19" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="136" t="s">
+      <c r="D19" s="139" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="136" t="s">
+      <c r="A20" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="136" t="s">
+      <c r="B20" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="136" t="s">
+      <c r="C20" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="136" t="s">
+      <c r="D20" s="139" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="136" t="s">
+      <c r="A21" s="139" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="136" t="s">
+      <c r="B21" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="136" t="s">
+      <c r="C21" s="139" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="136" t="s">
+      <c r="D21" s="139" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="136" t="s">
+      <c r="A22" s="139" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="136" t="s">
+      <c r="C22" s="139" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="136" t="s">
+      <c r="D22" s="139" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="139" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="136" t="s">
+      <c r="C23" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="136" t="s">
+      <c r="D23" s="139" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="136" t="s">
+      <c r="A24" s="139" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="136" t="s">
+      <c r="C24" s="139" t="s">
         <v>142</v>
       </c>
-      <c r="D24" s="136"/>
+      <c r="D24" s="139"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="136" t="s">
+      <c r="A25" s="139" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="136" t="s">
+      <c r="B25" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="136" t="s">
+      <c r="C25" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="136"/>
+      <c r="D25" s="139"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="136" t="s">
+      <c r="A26" s="139" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="136" t="s">
+      <c r="B26" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="136" t="s">
+      <c r="C26" s="139" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="136" t="s">
+      <c r="D26" s="139" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="136" t="s">
+      <c r="A27" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="136" t="s">
+      <c r="B27" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="139" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="136"/>
+      <c r="D27" s="139"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="136" t="s">
+      <c r="A28" s="139" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="136" t="s">
+      <c r="C28" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="136"/>
+      <c r="D28" s="139"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="136" t="s">
+      <c r="A29" s="139" t="s">
         <v>152</v>
       </c>
-      <c r="B29" s="136" t="s">
+      <c r="B29" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="136" t="s">
+      <c r="C29" s="139" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="136"/>
+      <c r="D29" s="139"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="136" t="s">
+      <c r="A30" s="139" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="136" t="s">
+      <c r="B30" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="136" t="s">
+      <c r="C30" s="139" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="136" t="s">
+      <c r="D30" s="139" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="136" t="s">
+      <c r="A31" s="139" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="136" t="s">
+      <c r="B31" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="136" t="s">
+      <c r="C31" s="139" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="136" t="s">
+      <c r="D31" s="139" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="136" t="s">
+      <c r="A32" s="139" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="136" t="s">
+      <c r="B32" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="136" t="s">
+      <c r="C32" s="139" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="136"/>
+      <c r="D32" s="139"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="136" t="s">
+      <c r="A33" s="139" t="s">
         <v>161</v>
       </c>
-      <c r="B33" s="136" t="s">
+      <c r="B33" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="136" t="s">
+      <c r="C33" s="139" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="136" t="s">
+      <c r="D33" s="139" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="136" t="s">
+      <c r="A34" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="B34" s="136" t="s">
+      <c r="B34" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="136" t="s">
+      <c r="C34" s="139" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="136" t="s">
+      <c r="D34" s="139" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="136" t="s">
+      <c r="A35" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="136" t="s">
+      <c r="B35" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="136" t="s">
+      <c r="C35" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="136" t="s">
+      <c r="D35" s="139" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="136" t="s">
+      <c r="A36" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="B36" s="136" t="s">
+      <c r="B36" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="136" t="s">
+      <c r="C36" s="139" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="136" t="s">
+      <c r="D36" s="139" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="136" t="s">
+      <c r="A37" s="139" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="136" t="s">
+      <c r="B37" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="136" t="s">
+      <c r="C37" s="139" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="136" t="s">
+      <c r="D37" s="139" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="136" t="s">
+      <c r="A38" s="139" t="s">
         <v>172</v>
       </c>
-      <c r="B38" s="136" t="s">
+      <c r="B38" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="136" t="s">
+      <c r="C38" s="139" t="s">
         <v>173</v>
       </c>
-      <c r="D38" s="136" t="s">
+      <c r="D38" s="139" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="136" t="s">
+      <c r="A39" s="139" t="s">
         <v>174</v>
       </c>
-      <c r="B39" s="136" t="s">
+      <c r="B39" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="136" t="s">
+      <c r="C39" s="139" t="s">
         <v>175</v>
       </c>
-      <c r="D39" s="136" t="s">
+      <c r="D39" s="139" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="136" t="s">
+      <c r="A40" s="139" t="s">
         <v>177</v>
       </c>
-      <c r="B40" s="136" t="s">
+      <c r="B40" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="136" t="s">
+      <c r="C40" s="139" t="s">
         <v>178</v>
       </c>
-      <c r="D40" s="136" t="s">
+      <c r="D40" s="139" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="137" t="s">
+      <c r="A41" s="140" t="s">
         <v>180</v>
       </c>
-      <c r="B41" s="137" t="s">
+      <c r="B41" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="137" t="s">
+      <c r="C41" s="140" t="s">
         <v>181</v>
       </c>
-      <c r="D41" s="137" t="s">
+      <c r="D41" s="140" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="137" t="s">
+      <c r="A42" s="140" t="s">
         <v>183</v>
       </c>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="137" t="s">
+      <c r="C42" s="140" t="s">
         <v>184</v>
       </c>
-      <c r="D42" s="137" t="s">
+      <c r="D42" s="140" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="138" t="s">
+      <c r="A43" s="141" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="139" t="s">
+      <c r="B43" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="138" t="s">
+      <c r="C43" s="141" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="138" t="s">
+      <c r="D43" s="141" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="138" t="s">
+      <c r="A44" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="B44" s="139" t="s">
+      <c r="B44" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="138" t="s">
+      <c r="C44" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="138" t="s">
+      <c r="D44" s="141" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="138" t="s">
+      <c r="A45" s="141" t="s">
         <v>190</v>
       </c>
-      <c r="B45" s="139" t="s">
+      <c r="B45" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="138" t="s">
+      <c r="C45" s="141" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="138"/>
+      <c r="D45" s="141"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="138" t="s">
+      <c r="A46" s="141" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="139" t="s">
+      <c r="B46" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="138" t="s">
+      <c r="C46" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="138"/>
+      <c r="D46" s="141"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="138" t="s">
+      <c r="A47" s="141" t="s">
         <v>194</v>
       </c>
-      <c r="B47" s="139" t="s">
+      <c r="B47" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="138" t="s">
+      <c r="C47" s="141" t="s">
         <v>195</v>
       </c>
-      <c r="D47" s="138"/>
+      <c r="D47" s="141"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="136" t="s">
+      <c r="A48" s="139" t="s">
         <v>196</v>
       </c>
-      <c r="B48" s="136" t="s">
+      <c r="B48" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="136" t="s">
+      <c r="C48" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="D48" s="136"/>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48" s="139"/>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -7671,32 +8058,32 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="138" t="s">
+      <c r="A50" s="141" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="139" t="s">
+      <c r="B50" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="138" t="s">
+      <c r="C50" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="D50" s="138" t="s">
+      <c r="D50" s="141" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="138" t="s">
+      <c r="A51" s="141" t="s">
         <v>203</v>
       </c>
-      <c r="B51" s="140" t="s">
+      <c r="B51" s="143" t="s">
         <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>204</v>
       </c>
-      <c r="D51" s="138"/>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51" s="141"/>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>205</v>
       </c>
@@ -7707,7 +8094,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>207</v>
       </c>
@@ -7718,7 +8105,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>209</v>
       </c>
@@ -7729,7 +8116,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>211</v>
       </c>
@@ -7740,7 +8127,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>213</v>
       </c>
@@ -7751,7 +8138,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>215</v>
       </c>
@@ -7762,7 +8149,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>217</v>
       </c>
@@ -7773,7 +8160,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>219</v>
       </c>
@@ -7784,7 +8171,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>221</v>
       </c>
@@ -7795,7 +8182,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>223</v>
       </c>
@@ -7806,7 +8193,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>225</v>
       </c>
@@ -7817,7 +8204,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>227</v>
       </c>
@@ -7828,7 +8215,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>229</v>
       </c>
@@ -7873,13 +8260,13 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="144" t="s">
         <v>237</v>
       </c>
-      <c r="B68" s="141" t="s">
+      <c r="B68" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="141" t="s">
+      <c r="C68" s="144" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7895,24 +8282,24 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="142" t="s">
+      <c r="A70" s="145" t="s">
         <v>241</v>
       </c>
-      <c r="B70" s="142" t="s">
+      <c r="B70" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="142" t="s">
+      <c r="C70" s="145" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="142" t="s">
+      <c r="A71" s="145" t="s">
         <v>243</v>
       </c>
-      <c r="B71" s="142" t="s">
+      <c r="B71" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="C71" s="143" t="s">
+      <c r="C71" s="146" t="s">
         <v>244</v>
       </c>
     </row>
@@ -8003,7 +8390,7 @@
     <col min="47" max="47" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46">
+    <row r="1" spans="1:47">
       <c r="A1" t="s">
         <v>251</v>
       </c>
@@ -8110,10 +8497,10 @@
       <c r="Z2">
         <v>1</v>
       </c>
-      <c r="AB2" s="123" t="s">
+      <c r="AB2" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AC2" s="123">
+      <c r="AC2" s="121">
         <v>1</v>
       </c>
       <c r="AE2" t="s">
@@ -8153,7 +8540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="4:47">
+    <row r="3" spans="1:47">
       <c r="D3" t="s">
         <v>283</v>
       </c>
@@ -8196,10 +8583,10 @@
       <c r="Z3">
         <v>2</v>
       </c>
-      <c r="AB3" s="123" t="s">
+      <c r="AB3" s="121" t="s">
         <v>290</v>
       </c>
-      <c r="AC3" s="123">
+      <c r="AC3" s="121">
         <v>2</v>
       </c>
       <c r="AE3" t="s">
@@ -8239,14 +8626,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="4:47">
+    <row r="4" spans="1:47">
       <c r="D4" t="s">
         <v>297</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="G4" s="118" t="s">
+      <c r="G4" s="122" t="s">
         <v>298</v>
       </c>
       <c r="H4">
@@ -8282,10 +8669,10 @@
       <c r="Z4">
         <v>3</v>
       </c>
-      <c r="AB4" s="123" t="s">
+      <c r="AB4" s="121" t="s">
         <v>304</v>
       </c>
-      <c r="AC4" s="123">
+      <c r="AC4" s="121">
         <v>3</v>
       </c>
       <c r="AE4" t="s">
@@ -8325,14 +8712,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="4:47">
+    <row r="5" spans="1:47">
       <c r="D5" t="s">
         <v>311</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="G5" s="118" t="s">
+      <c r="G5" s="122" t="s">
         <v>312</v>
       </c>
       <c r="H5">
@@ -8368,10 +8755,10 @@
       <c r="Z5">
         <v>4</v>
       </c>
-      <c r="AB5" s="124" t="s">
+      <c r="AB5" s="123" t="s">
         <v>318</v>
       </c>
-      <c r="AC5" s="123">
+      <c r="AC5" s="121">
         <v>4</v>
       </c>
       <c r="AE5" t="s">
@@ -8399,14 +8786,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="4:47">
+    <row r="6" spans="1:47">
       <c r="D6" t="s">
         <v>323</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
-      <c r="G6" s="119" t="s">
+      <c r="G6" s="124" t="s">
         <v>324</v>
       </c>
       <c r="H6">
@@ -8436,10 +8823,10 @@
       <c r="Z6">
         <v>5</v>
       </c>
-      <c r="AB6" s="123" t="s">
+      <c r="AB6" s="121" t="s">
         <v>329</v>
       </c>
-      <c r="AC6" s="123">
+      <c r="AC6" s="121">
         <v>5</v>
       </c>
       <c r="AE6" t="s">
@@ -8467,14 +8854,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="4:47">
+    <row r="7" spans="1:47">
       <c r="D7" t="s">
         <v>334</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
-      <c r="G7" s="119" t="s">
+      <c r="G7" s="124" t="s">
         <v>335</v>
       </c>
       <c r="H7">
@@ -8501,7 +8888,7 @@
       <c r="AB7" s="125" t="s">
         <v>338</v>
       </c>
-      <c r="AC7" s="123">
+      <c r="AC7" s="121">
         <v>6</v>
       </c>
       <c r="AE7" t="s">
@@ -8529,14 +8916,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="4:44">
+    <row r="8" spans="1:47">
       <c r="D8" t="s">
         <v>343</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="126" t="s">
         <v>344</v>
       </c>
       <c r="H8">
@@ -8548,7 +8935,7 @@
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="P8" s="122" t="s">
+      <c r="P8" s="127" t="s">
         <v>346</v>
       </c>
       <c r="Q8">
@@ -8560,10 +8947,10 @@
       <c r="W8">
         <v>7</v>
       </c>
-      <c r="AB8" s="123" t="s">
+      <c r="AB8" s="121" t="s">
         <v>348</v>
       </c>
-      <c r="AC8" s="123">
+      <c r="AC8" s="121">
         <v>7</v>
       </c>
       <c r="AE8" t="s">
@@ -8585,14 +8972,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="4:44">
+    <row r="9" spans="1:47">
       <c r="D9" t="s">
         <v>352</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="126" t="s">
         <v>353</v>
       </c>
       <c r="H9">
@@ -8610,10 +8997,10 @@
       <c r="W9">
         <v>8</v>
       </c>
-      <c r="AB9" s="123" t="s">
+      <c r="AB9" s="121" t="s">
         <v>356</v>
       </c>
-      <c r="AC9" s="123">
+      <c r="AC9" s="121">
         <v>8</v>
       </c>
       <c r="AQ9" s="24" t="s">
@@ -8623,7 +9010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="7:44">
+    <row r="10" spans="1:47">
       <c r="G10" s="52" t="s">
         <v>358</v>
       </c>
@@ -8642,10 +9029,10 @@
       <c r="W10">
         <v>9</v>
       </c>
-      <c r="AB10" s="123" t="s">
+      <c r="AB10" s="121" t="s">
         <v>361</v>
       </c>
-      <c r="AC10" s="123">
+      <c r="AC10" s="121">
         <v>9</v>
       </c>
       <c r="AQ10" s="24" t="s">
@@ -8655,14 +9042,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="7:44">
+    <row r="11" spans="1:47">
       <c r="G11" s="52" t="s">
         <v>363</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="M11" s="122" t="s">
+      <c r="M11" s="127" t="s">
         <v>364</v>
       </c>
       <c r="N11">
@@ -8674,10 +9061,10 @@
       <c r="W11">
         <v>10</v>
       </c>
-      <c r="AB11" s="123" t="s">
+      <c r="AB11" s="121" t="s">
         <v>366</v>
       </c>
-      <c r="AC11" s="123">
+      <c r="AC11" s="121">
         <v>10</v>
       </c>
       <c r="AQ11" s="24" t="s">
@@ -8687,17 +9074,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="7:44">
-      <c r="G12" s="118" t="s">
+    <row r="12" spans="1:47">
+      <c r="G12" s="122" t="s">
         <v>368</v>
       </c>
       <c r="H12">
         <v>11</v>
       </c>
-      <c r="AB12" s="124" t="s">
+      <c r="AB12" s="123" t="s">
         <v>369</v>
       </c>
-      <c r="AC12" s="126">
+      <c r="AC12" s="128">
         <v>11</v>
       </c>
       <c r="AQ12" s="24" t="s">
@@ -8707,17 +9094,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="7:44">
-      <c r="G13" s="118" t="s">
+    <row r="13" spans="1:47">
+      <c r="G13" s="122" t="s">
         <v>371</v>
       </c>
       <c r="H13">
         <v>12</v>
       </c>
-      <c r="AB13" s="123" t="s">
+      <c r="AB13" s="121" t="s">
         <v>372</v>
       </c>
-      <c r="AC13" s="123">
+      <c r="AC13" s="121">
         <v>12</v>
       </c>
       <c r="AQ13" s="24" t="s">
@@ -8727,17 +9114,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="7:44">
+    <row r="14" spans="1:47">
       <c r="G14" s="53" t="s">
         <v>374</v>
       </c>
       <c r="H14">
         <v>13</v>
       </c>
-      <c r="AB14" s="123" t="s">
+      <c r="AB14" s="121" t="s">
         <v>375</v>
       </c>
-      <c r="AC14" s="123">
+      <c r="AC14" s="121">
         <v>13</v>
       </c>
       <c r="AQ14" s="24" t="s">
@@ -8747,17 +9134,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="7:44">
+    <row r="15" spans="1:47">
       <c r="G15" s="53" t="s">
         <v>377</v>
       </c>
       <c r="H15">
         <v>14</v>
       </c>
-      <c r="AB15" s="123" t="s">
+      <c r="AB15" s="121" t="s">
         <v>378</v>
       </c>
-      <c r="AC15" s="123">
+      <c r="AC15" s="121">
         <v>14</v>
       </c>
       <c r="AQ15" s="24" t="s">
@@ -8767,17 +9154,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="7:44">
+    <row r="16" spans="1:47">
       <c r="G16" s="52" t="s">
         <v>380</v>
       </c>
       <c r="H16">
         <v>15</v>
       </c>
-      <c r="AB16" s="127" t="s">
+      <c r="AB16" s="129" t="s">
         <v>381</v>
       </c>
-      <c r="AC16" s="123">
+      <c r="AC16" s="121">
         <v>15</v>
       </c>
       <c r="AQ16" s="24" t="s">
@@ -8794,10 +9181,10 @@
       <c r="H17">
         <v>16</v>
       </c>
-      <c r="AB17" s="128" t="s">
+      <c r="AB17" s="130" t="s">
         <v>384</v>
       </c>
-      <c r="AC17" s="123">
+      <c r="AC17" s="121">
         <v>16</v>
       </c>
       <c r="AQ17" s="24" t="s">
@@ -8808,16 +9195,16 @@
       </c>
     </row>
     <row r="18" spans="7:44">
-      <c r="G18" s="121" t="s">
+      <c r="G18" s="131" t="s">
         <v>386</v>
       </c>
       <c r="H18">
         <v>17</v>
       </c>
-      <c r="AB18" s="128" t="s">
+      <c r="AB18" s="130" t="s">
         <v>387</v>
       </c>
-      <c r="AC18" s="123">
+      <c r="AC18" s="121">
         <v>17</v>
       </c>
       <c r="AQ18" s="24" t="s">
@@ -8828,16 +9215,16 @@
       </c>
     </row>
     <row r="19" spans="7:44">
-      <c r="G19" s="121" t="s">
+      <c r="G19" s="131" t="s">
         <v>389</v>
       </c>
       <c r="H19">
         <v>18</v>
       </c>
-      <c r="AB19" s="128" t="s">
+      <c r="AB19" s="130" t="s">
         <v>390</v>
       </c>
-      <c r="AC19" s="123">
+      <c r="AC19" s="121">
         <v>18</v>
       </c>
       <c r="AE19" s="57"/>
@@ -8849,16 +9236,16 @@
       </c>
     </row>
     <row r="20" spans="7:44">
-      <c r="G20" s="121" t="s">
+      <c r="G20" s="131" t="s">
         <v>392</v>
       </c>
       <c r="H20">
         <v>19</v>
       </c>
-      <c r="AB20" s="129" t="s">
+      <c r="AB20" s="132" t="s">
         <v>393</v>
       </c>
-      <c r="AC20" s="128">
+      <c r="AC20" s="130">
         <v>19</v>
       </c>
       <c r="AQ20" s="24" t="s">
@@ -8869,16 +9256,16 @@
       </c>
     </row>
     <row r="21" spans="7:44">
-      <c r="G21" s="121" t="s">
+      <c r="G21" s="131" t="s">
         <v>395</v>
       </c>
       <c r="H21">
         <v>20</v>
       </c>
-      <c r="AB21" s="126" t="s">
+      <c r="AB21" s="128" t="s">
         <v>396</v>
       </c>
-      <c r="AC21" s="123">
+      <c r="AC21" s="121">
         <v>20</v>
       </c>
       <c r="AQ21" s="24" t="s">
@@ -8895,10 +9282,10 @@
       <c r="H22">
         <v>21</v>
       </c>
-      <c r="AB22" s="20" t="s">
+      <c r="AB22" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="AC22" s="20">
+      <c r="AC22" s="18">
         <v>21</v>
       </c>
       <c r="AQ22" s="24" t="s">
@@ -8909,16 +9296,16 @@
       </c>
     </row>
     <row r="23" spans="7:44">
-      <c r="G23" s="121" t="s">
+      <c r="G23" s="131" t="s">
         <v>401</v>
       </c>
       <c r="H23" s="21">
         <v>22</v>
       </c>
-      <c r="AB23" s="20" t="s">
+      <c r="AB23" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="AC23" s="20">
+      <c r="AC23" s="18">
         <v>22</v>
       </c>
       <c r="AQ23" s="24" t="s">
@@ -8935,10 +9322,10 @@
       <c r="H24">
         <v>23</v>
       </c>
-      <c r="AB24" s="130" t="s">
+      <c r="AB24" s="133" t="s">
         <v>405</v>
       </c>
-      <c r="AC24" s="130">
+      <c r="AC24" s="133">
         <v>23</v>
       </c>
       <c r="AQ24" s="24" t="s">
@@ -8955,10 +9342,10 @@
       <c r="H25">
         <v>24</v>
       </c>
-      <c r="AB25" s="130" t="s">
+      <c r="AB25" s="133" t="s">
         <v>408</v>
       </c>
-      <c r="AC25" s="130">
+      <c r="AC25" s="133">
         <v>24</v>
       </c>
       <c r="AQ25" s="24" t="s">
@@ -8975,10 +9362,10 @@
       <c r="H26">
         <v>25</v>
       </c>
-      <c r="AB26" s="130" t="s">
+      <c r="AB26" s="133" t="s">
         <v>411</v>
       </c>
-      <c r="AC26" s="130">
+      <c r="AC26" s="133">
         <v>25</v>
       </c>
       <c r="AQ26" s="24" t="s">
@@ -8989,16 +9376,16 @@
       </c>
     </row>
     <row r="27" spans="7:44">
-      <c r="G27" s="118" t="s">
+      <c r="G27" s="122" t="s">
         <v>413</v>
       </c>
       <c r="H27">
         <v>26</v>
       </c>
-      <c r="AB27" s="131" t="s">
+      <c r="AB27" s="134" t="s">
         <v>414</v>
       </c>
-      <c r="AC27" s="130">
+      <c r="AC27" s="133">
         <v>26</v>
       </c>
       <c r="AQ27" s="24" t="s">
@@ -9009,7 +9396,7 @@
       </c>
     </row>
     <row r="28" spans="7:44">
-      <c r="G28" s="118" t="s">
+      <c r="G28" s="122" t="s">
         <v>416</v>
       </c>
       <c r="H28">
@@ -9018,7 +9405,7 @@
       <c r="AB28" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="AC28" s="130">
+      <c r="AC28" s="133">
         <v>27</v>
       </c>
       <c r="AQ28" s="24" t="s">
@@ -9035,10 +9422,10 @@
       <c r="H29" s="22">
         <v>28</v>
       </c>
-      <c r="AB29" s="130" t="s">
+      <c r="AB29" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="AC29" s="130">
+      <c r="AC29" s="133">
         <v>28</v>
       </c>
       <c r="AQ29" s="24" t="s">
@@ -9055,10 +9442,10 @@
       <c r="H30">
         <v>29</v>
       </c>
-      <c r="AB30" s="130" t="s">
+      <c r="AB30" s="133" t="s">
         <v>423</v>
       </c>
-      <c r="AC30" s="130">
+      <c r="AC30" s="133">
         <v>29</v>
       </c>
       <c r="AQ30" s="24" t="s">
@@ -9075,10 +9462,10 @@
       <c r="H31">
         <v>30</v>
       </c>
-      <c r="AB31" s="130" t="s">
+      <c r="AB31" s="133" t="s">
         <v>426</v>
       </c>
-      <c r="AC31" s="130">
+      <c r="AC31" s="133">
         <v>30</v>
       </c>
       <c r="AQ31" s="24" t="s">
@@ -9117,7 +9504,7 @@
       </c>
     </row>
     <row r="34" spans="7:44">
-      <c r="G34" s="121" t="s">
+      <c r="G34" s="131" t="s">
         <v>432</v>
       </c>
       <c r="H34">
@@ -9327,7 +9714,7 @@
       </c>
     </row>
     <row r="49" spans="7:44">
-      <c r="G49" s="118" t="s">
+      <c r="G49" s="122" t="s">
         <v>462</v>
       </c>
       <c r="H49">
@@ -9341,7 +9728,7 @@
       </c>
     </row>
     <row r="50" spans="7:44">
-      <c r="G50" s="118" t="s">
+      <c r="G50" s="122" t="s">
         <v>464</v>
       </c>
       <c r="H50">
@@ -9411,7 +9798,7 @@
       </c>
     </row>
     <row r="55" spans="7:44">
-      <c r="G55" s="121" t="s">
+      <c r="G55" s="131" t="s">
         <v>474</v>
       </c>
       <c r="H55">
@@ -9467,7 +9854,7 @@
       </c>
     </row>
     <row r="59" spans="7:44">
-      <c r="G59" s="121" t="s">
+      <c r="G59" s="131" t="s">
         <v>482</v>
       </c>
       <c r="H59">
@@ -9481,13 +9868,13 @@
       </c>
     </row>
     <row r="60" spans="7:44">
-      <c r="G60" s="121" t="s">
+      <c r="G60" s="131" t="s">
         <v>484</v>
       </c>
       <c r="H60">
         <v>59</v>
       </c>
-      <c r="AQ60" s="132" t="s">
+      <c r="AQ60" s="135" t="s">
         <v>485</v>
       </c>
       <c r="AR60" s="24">
@@ -9495,13 +9882,13 @@
       </c>
     </row>
     <row r="61" spans="7:44">
-      <c r="G61" s="121" t="s">
+      <c r="G61" s="131" t="s">
         <v>486</v>
       </c>
       <c r="H61">
         <v>60</v>
       </c>
-      <c r="AQ61" s="132" t="s">
+      <c r="AQ61" s="135" t="s">
         <v>487</v>
       </c>
       <c r="AR61" s="24">
@@ -9515,7 +9902,7 @@
       <c r="H62">
         <v>61</v>
       </c>
-      <c r="AQ62" s="133" t="s">
+      <c r="AQ62" s="136" t="s">
         <v>489</v>
       </c>
       <c r="AR62" s="16">
@@ -9530,7 +9917,7 @@
         <v>62</v>
       </c>
       <c r="J63" s="15"/>
-      <c r="AQ63" s="133" t="s">
+      <c r="AQ63" s="136" t="s">
         <v>491</v>
       </c>
       <c r="AR63" s="16">
@@ -9544,7 +9931,7 @@
       <c r="H64">
         <v>63</v>
       </c>
-      <c r="AQ64" s="133" t="s">
+      <c r="AQ64" s="136" t="s">
         <v>493</v>
       </c>
       <c r="AR64" s="16">
@@ -9558,7 +9945,7 @@
       <c r="H65">
         <v>64</v>
       </c>
-      <c r="AQ65" s="133" t="s">
+      <c r="AQ65" s="136" t="s">
         <v>495</v>
       </c>
       <c r="AR65" s="16">
@@ -9566,13 +9953,13 @@
       </c>
     </row>
     <row r="66" spans="7:44">
-      <c r="G66" s="118" t="s">
+      <c r="G66" s="122" t="s">
         <v>496</v>
       </c>
       <c r="H66">
         <v>65</v>
       </c>
-      <c r="AQ66" s="133" t="s">
+      <c r="AQ66" s="136" t="s">
         <v>497</v>
       </c>
       <c r="AR66" s="16">
@@ -9580,13 +9967,13 @@
       </c>
     </row>
     <row r="67" spans="7:44">
-      <c r="G67" s="118" t="s">
+      <c r="G67" s="122" t="s">
         <v>498</v>
       </c>
       <c r="H67">
         <v>66</v>
       </c>
-      <c r="AQ67" s="133" t="s">
+      <c r="AQ67" s="136" t="s">
         <v>499</v>
       </c>
       <c r="AR67" s="16">
@@ -9594,13 +9981,13 @@
       </c>
     </row>
     <row r="68" spans="7:44">
-      <c r="G68" s="118" t="s">
+      <c r="G68" s="122" t="s">
         <v>500</v>
       </c>
       <c r="H68">
         <v>67</v>
       </c>
-      <c r="AQ68" s="133" t="s">
+      <c r="AQ68" s="136" t="s">
         <v>501</v>
       </c>
       <c r="AR68" s="16">
@@ -9608,13 +9995,13 @@
       </c>
     </row>
     <row r="69" spans="7:44">
-      <c r="G69" s="118" t="s">
+      <c r="G69" s="122" t="s">
         <v>502</v>
       </c>
       <c r="H69">
         <v>68</v>
       </c>
-      <c r="AQ69" s="135" t="s">
+      <c r="AQ69" s="137" t="s">
         <v>503</v>
       </c>
       <c r="AR69" s="24">
@@ -9628,7 +10015,7 @@
       <c r="H70">
         <v>69</v>
       </c>
-      <c r="AQ70" s="135" t="s">
+      <c r="AQ70" s="137" t="s">
         <v>505</v>
       </c>
       <c r="AR70" s="24">
@@ -9642,7 +10029,7 @@
       <c r="H71">
         <v>70</v>
       </c>
-      <c r="AQ71" s="133" t="s">
+      <c r="AQ71" s="136" t="s">
         <v>507</v>
       </c>
       <c r="AR71" s="24">
@@ -9656,7 +10043,7 @@
       <c r="H72">
         <v>71</v>
       </c>
-      <c r="AQ72" s="133" t="s">
+      <c r="AQ72" s="136" t="s">
         <v>509</v>
       </c>
       <c r="AR72" s="24">
@@ -9670,7 +10057,7 @@
       <c r="H73">
         <v>72</v>
       </c>
-      <c r="AQ73" s="133" t="s">
+      <c r="AQ73" s="136" t="s">
         <v>511</v>
       </c>
       <c r="AR73" s="16">
@@ -9678,13 +10065,13 @@
       </c>
     </row>
     <row r="74" spans="7:44">
-      <c r="G74" s="118" t="s">
+      <c r="G74" s="122" t="s">
         <v>512</v>
       </c>
       <c r="H74">
         <v>73</v>
       </c>
-      <c r="AQ74" s="133" t="s">
+      <c r="AQ74" s="136" t="s">
         <v>513</v>
       </c>
       <c r="AR74" s="16">
@@ -9692,13 +10079,13 @@
       </c>
     </row>
     <row r="75" spans="7:44">
-      <c r="G75" s="134" t="s">
+      <c r="G75" s="138" t="s">
         <v>514</v>
       </c>
       <c r="H75">
         <v>74</v>
       </c>
-      <c r="AQ75" s="133" t="s">
+      <c r="AQ75" s="136" t="s">
         <v>515</v>
       </c>
       <c r="AR75" s="16">
@@ -9712,7 +10099,7 @@
       <c r="H76">
         <v>75</v>
       </c>
-      <c r="AQ76" s="133" t="s">
+      <c r="AQ76" s="136" t="s">
         <v>517</v>
       </c>
       <c r="AR76" s="16">
@@ -9726,14 +10113,14 @@
       <c r="H77">
         <v>76</v>
       </c>
-      <c r="AQ77" s="133" t="s">
+      <c r="AQ77" s="136" t="s">
         <v>519</v>
       </c>
       <c r="AR77" s="16">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="7:8">
+    <row r="78" spans="7:44">
       <c r="G78" s="46" t="s">
         <v>520</v>
       </c>
@@ -9741,7 +10128,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="7:8">
+    <row r="79" spans="7:44">
       <c r="G79" t="s">
         <v>521</v>
       </c>
@@ -9749,7 +10136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="7:8">
+    <row r="80" spans="7:44">
       <c r="G80" t="s">
         <v>522</v>
       </c>
@@ -9870,6 +10257,309 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="20.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="18.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="11.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="118" t="s">
+        <v>538</v>
+      </c>
+      <c r="B2" s="119" t="s">
+        <v>539</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="119">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="118"/>
+      <c r="B3" s="119" t="s">
+        <v>540</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="119">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="118"/>
+      <c r="B4" s="119" t="s">
+        <v>541</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="119">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="118"/>
+      <c r="B5" s="119" t="s">
+        <v>542</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="119">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="118"/>
+      <c r="B6" s="119" t="s">
+        <v>543</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="119">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="118"/>
+      <c r="B7" s="119" t="s">
+        <v>544</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="119">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="120"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="118" t="s">
+        <v>545</v>
+      </c>
+      <c r="B9" s="119" t="s">
+        <v>546</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="119">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="118"/>
+      <c r="B10" s="119" t="s">
+        <v>547</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="119">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="118"/>
+      <c r="B11" s="119" t="s">
+        <v>548</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="118"/>
+      <c r="B12" s="119" t="s">
+        <v>549</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="119">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="118"/>
+      <c r="B13" s="119" t="s">
+        <v>550</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="119" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="118"/>
+      <c r="B14" s="119" t="s">
+        <v>552</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="120"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="118" t="s">
+        <v>554</v>
+      </c>
+      <c r="B16" s="119" t="s">
+        <v>555</v>
+      </c>
+      <c r="C16" t="s">
+        <v>556</v>
+      </c>
+      <c r="D16" s="119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="118"/>
+      <c r="B17" s="119" t="s">
+        <v>557</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="118"/>
+      <c r="B18" s="119" t="s">
+        <v>559</v>
+      </c>
+      <c r="C18" t="s">
+        <v>556</v>
+      </c>
+      <c r="D18" s="119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="118"/>
+      <c r="B19" s="119" t="s">
+        <v>560</v>
+      </c>
+      <c r="C19" t="s">
+        <v>556</v>
+      </c>
+      <c r="D19" s="119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="118"/>
+      <c r="B20" s="119" t="s">
+        <v>561</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="119">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="118"/>
+      <c r="B21" s="119" t="s">
+        <v>562</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="119" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="120"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" t="s">
+        <v>564</v>
+      </c>
+      <c r="C23" t="s">
+        <v>565</v>
+      </c>
+      <c r="D23" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
+        <v>567</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>568</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A16:A21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H2"/>
@@ -9890,25 +10580,25 @@
         <v>250</v>
       </c>
       <c r="B1" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="C1" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="D1" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="E1" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="F1" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="G1" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="H1" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9916,7 +10606,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -9944,7 +10634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O31"/>
@@ -9973,46 +10663,46 @@
         <v>250</v>
       </c>
       <c r="B1" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" s="71" customFormat="1" spans="1:15">
@@ -10020,7 +10710,7 @@
         <v>276</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="C2" s="71">
         <v>102</v>
@@ -10038,7 +10728,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="71" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="I2" s="71">
         <v>2</v>
@@ -10069,7 +10759,7 @@
         <v>290</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="C3" s="72">
         <v>160</v>
@@ -10087,7 +10777,7 @@
         <v>100</v>
       </c>
       <c r="H3" s="72" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
       <c r="I3" s="72">
         <v>3</v>
@@ -10118,7 +10808,7 @@
         <v>304</v>
       </c>
       <c r="B4" s="73" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="C4" s="73">
         <v>210</v>
@@ -10136,7 +10826,7 @@
         <v>100</v>
       </c>
       <c r="H4" s="73" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="I4" s="73">
         <v>3</v>
@@ -10167,7 +10857,7 @@
         <v>318</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="C5" s="93">
         <v>3300</v>
@@ -10185,7 +10875,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="74" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="I5" s="74">
         <v>40</v>
@@ -10215,7 +10905,7 @@
         <v>329</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="C6" s="75">
         <v>360</v>
@@ -10233,7 +10923,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="75" t="s">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="I6" s="75">
         <v>5</v>
@@ -10264,7 +10954,7 @@
         <v>338</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="C7" s="93">
         <v>3300</v>
@@ -10282,7 +10972,7 @@
         <v>100</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="I7" s="76">
         <v>40</v>
@@ -10312,7 +11002,7 @@
         <v>348</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>565</v>
+        <v>597</v>
       </c>
       <c r="C8" s="77">
         <v>320</v>
@@ -10330,7 +11020,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="77" t="s">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="I8" s="77">
         <v>4</v>
@@ -10361,7 +11051,7 @@
         <v>356</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="C9" s="71">
         <v>210</v>
@@ -10379,7 +11069,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="71" t="s">
-        <v>568</v>
+        <v>600</v>
       </c>
       <c r="I9" s="71">
         <v>4</v>
@@ -10410,7 +11100,7 @@
         <v>361</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="C10" s="73">
         <v>180</v>
@@ -10428,7 +11118,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="73" t="s">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="I10" s="73">
         <v>5</v>
@@ -10459,7 +11149,7 @@
         <v>366</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>571</v>
+        <v>603</v>
       </c>
       <c r="C11" s="78">
         <v>210</v>
@@ -10477,7 +11167,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="78" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="I11" s="78">
         <v>5</v>
@@ -10508,7 +11198,7 @@
         <v>369</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="C12" s="93">
         <v>3300</v>
@@ -10526,7 +11216,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="74" t="s">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="I12" s="74">
         <v>40</v>
@@ -10556,7 +11246,7 @@
         <v>372</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="C13" s="71">
         <v>300</v>
@@ -10574,7 +11264,7 @@
         <v>100</v>
       </c>
       <c r="H13" s="71" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="I13" s="71">
         <v>5</v>
@@ -10605,7 +11295,7 @@
         <v>375</v>
       </c>
       <c r="B14" s="79" t="s">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="C14" s="79">
         <v>300</v>
@@ -10623,7 +11313,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="79" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="I14" s="79">
         <v>6</v>
@@ -10654,7 +11344,7 @@
         <v>378</v>
       </c>
       <c r="B15" s="73" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="C15" s="73">
         <v>270</v>
@@ -10672,7 +11362,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="73" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="I15" s="73">
         <v>6</v>
@@ -10703,7 +11393,7 @@
         <v>381</v>
       </c>
       <c r="B16" s="80" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="C16" s="93">
         <v>3300</v>
@@ -10721,7 +11411,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="80" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="I16" s="80">
         <v>40</v>
@@ -10751,7 +11441,7 @@
         <v>384</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="C17" s="81">
         <v>550</v>
@@ -10769,7 +11459,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="81" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
       <c r="I17" s="81">
         <v>9</v>
@@ -10800,7 +11490,7 @@
         <v>387</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="C18" s="82">
         <v>500</v>
@@ -10818,7 +11508,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="82" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="I18" s="82">
         <v>9</v>
@@ -10849,7 +11539,7 @@
         <v>390</v>
       </c>
       <c r="B19" s="83" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="C19" s="83">
         <v>550</v>
@@ -10867,7 +11557,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="83" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="I19" s="83">
         <v>9</v>
@@ -10898,7 +11588,7 @@
         <v>393</v>
       </c>
       <c r="B20" s="84" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="C20" s="93">
         <v>3300</v>
@@ -10916,7 +11606,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="84" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="I20" s="84">
         <v>40</v>
@@ -10946,7 +11636,7 @@
         <v>396</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="C21" s="15">
         <v>1000</v>
@@ -10964,7 +11654,7 @@
         <v>100</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>592</v>
+        <v>624</v>
       </c>
       <c r="I21" s="15">
         <v>0</v>
@@ -10995,7 +11685,7 @@
         <v>399</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="C22" s="15">
         <v>1000</v>
@@ -11013,7 +11703,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="I22" s="15">
         <v>0</v>
@@ -11044,7 +11734,7 @@
         <v>402</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="C23" s="15">
         <v>1000</v>
@@ -11062,7 +11752,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="I23" s="15">
         <v>0</v>
@@ -11093,7 +11783,7 @@
         <v>405</v>
       </c>
       <c r="B24" s="85" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="C24" s="93">
         <v>3500</v>
@@ -11111,7 +11801,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="85" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="I24" s="85">
         <v>40</v>
@@ -11141,7 +11831,7 @@
         <v>408</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="C25" s="93">
         <v>3500</v>
@@ -11159,7 +11849,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="85" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="I25" s="85">
         <v>40</v>
@@ -11189,7 +11879,7 @@
         <v>411</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="C26" s="93">
         <v>3300</v>
@@ -11207,7 +11897,7 @@
         <v>100</v>
       </c>
       <c r="H26" s="85" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="I26" s="85">
         <v>40</v>
@@ -11237,7 +11927,7 @@
         <v>414</v>
       </c>
       <c r="B27" s="57" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="C27" s="93">
         <v>3300</v>
@@ -11255,7 +11945,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="57" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="I27" s="57">
         <v>40</v>
@@ -11285,7 +11975,7 @@
         <v>417</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="C28" s="15">
         <v>450</v>
@@ -11303,7 +11993,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
@@ -11334,7 +12024,7 @@
         <v>420</v>
       </c>
       <c r="B29" s="57" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="C29" s="93">
         <v>3300</v>
@@ -11352,7 +12042,7 @@
         <v>100</v>
       </c>
       <c r="H29" s="57" t="s">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="I29" s="57">
         <v>40</v>
@@ -11382,7 +12072,7 @@
         <v>423</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="C30" s="117">
         <v>2100</v>
@@ -11400,7 +12090,7 @@
         <v>100</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="I30" s="15">
         <v>20</v>
@@ -11430,7 +12120,7 @@
         <v>426</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="C31" s="117">
         <v>2100</v>
@@ -11448,7 +12138,7 @@
         <v>100</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="I31" s="15">
         <v>20</v>
@@ -11483,7 +12173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N98"/>
@@ -11506,54 +12196,54 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="B1" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="C1" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="D1" t="s">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="E1" t="s">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="F1" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="G1" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="H1" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="I1" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="J1" t="s">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="K1" t="s">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="L1" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="M1" t="s">
-        <v>620</v>
+        <v>652</v>
       </c>
       <c r="N1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" s="46" customFormat="1" spans="1:12">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" s="46" customFormat="1" spans="1:14">
       <c r="A2" s="46" t="s">
         <v>276</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="C2" s="46" t="b">
         <f t="shared" ref="C2:C13" si="0">FALSE()</f>
@@ -11578,12 +12268,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="47" customFormat="1" spans="1:12">
+    <row r="3" s="47" customFormat="1" spans="1:14">
       <c r="A3" s="47" t="s">
         <v>290</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="C3" s="47" t="b">
         <f t="shared" si="0"/>
@@ -11608,12 +12298,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="48" customFormat="1" spans="1:12">
+    <row r="4" s="48" customFormat="1" spans="1:14">
       <c r="A4" s="48" t="s">
         <v>304</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="C4" s="48" t="b">
         <f t="shared" si="0"/>
@@ -11638,12 +12328,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" s="49" customFormat="1" spans="1:12">
+    <row r="5" s="49" customFormat="1" spans="1:14">
       <c r="A5" s="58" t="s">
         <v>318</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="C5" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11674,10 +12364,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" s="49" customFormat="1" spans="1:12">
+    <row r="6" s="49" customFormat="1" spans="1:14">
       <c r="A6" s="58"/>
       <c r="B6" s="49" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="C6" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11708,10 +12398,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" s="49" customFormat="1" spans="1:12">
+    <row r="7" s="49" customFormat="1" spans="1:14">
       <c r="A7" s="58"/>
       <c r="B7" s="49" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="C7" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11742,10 +12432,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" s="49" customFormat="1" spans="1:12">
+    <row r="8" s="49" customFormat="1" spans="1:14">
       <c r="A8" s="58"/>
       <c r="B8" s="49" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="C8" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11776,10 +12466,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" s="49" customFormat="1" spans="1:12">
+    <row r="9" s="49" customFormat="1" spans="1:14">
       <c r="A9" s="58"/>
       <c r="B9" s="49" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="C9" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11810,10 +12500,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" s="49" customFormat="1" spans="1:12">
+    <row r="10" s="49" customFormat="1" spans="1:14">
       <c r="A10" s="58"/>
       <c r="B10" s="49" t="s">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="C10" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11844,10 +12534,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" s="49" customFormat="1" spans="1:12">
+    <row r="11" s="49" customFormat="1" spans="1:14">
       <c r="A11" s="58"/>
       <c r="B11" s="49" t="s">
-        <v>631</v>
+        <v>663</v>
       </c>
       <c r="C11" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11878,10 +12568,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" s="49" customFormat="1" spans="1:12">
+    <row r="12" s="49" customFormat="1" spans="1:14">
       <c r="A12" s="58"/>
       <c r="B12" s="49" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="C12" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11912,10 +12602,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" s="49" customFormat="1" spans="1:12">
+    <row r="13" s="49" customFormat="1" spans="1:14">
       <c r="A13" s="58"/>
       <c r="B13" s="49" t="s">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="C13" s="49" t="b">
         <f t="shared" si="0"/>
@@ -11946,12 +12636,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" s="46" customFormat="1" spans="1:12">
+    <row r="14" s="46" customFormat="1" spans="1:14">
       <c r="A14" s="46" t="s">
         <v>356</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="C14" s="46" t="b">
         <f t="shared" ref="C14:C23" si="1">TRUE()</f>
@@ -11976,12 +12666,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" s="48" customFormat="1" spans="1:12">
+    <row r="15" s="48" customFormat="1" spans="1:14">
       <c r="A15" s="48" t="s">
         <v>361</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>635</v>
+        <v>667</v>
       </c>
       <c r="C15" s="48" t="b">
         <f t="shared" si="1"/>
@@ -12006,12 +12696,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" s="50" customFormat="1" spans="1:12">
+    <row r="16" s="50" customFormat="1" spans="1:14">
       <c r="A16" s="50" t="s">
         <v>366</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="C16" s="50" t="b">
         <f t="shared" si="1"/>
@@ -12036,12 +12726,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" s="49" customFormat="1" spans="1:13">
+    <row r="17" s="49" customFormat="1" spans="1:14">
       <c r="A17" s="58" t="s">
         <v>369</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="C17" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12075,10 +12765,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" s="49" customFormat="1" spans="1:12">
+    <row r="18" s="49" customFormat="1" spans="1:14">
       <c r="A18" s="58"/>
       <c r="B18" s="49" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="C18" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12109,10 +12799,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" s="49" customFormat="1" spans="1:12">
+    <row r="19" s="49" customFormat="1" spans="1:14">
       <c r="A19" s="58"/>
       <c r="B19" s="49" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="C19" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12143,10 +12833,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" s="49" customFormat="1" spans="1:12">
+    <row r="20" s="49" customFormat="1" spans="1:14">
       <c r="A20" s="58"/>
       <c r="B20" s="49" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="C20" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12177,10 +12867,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" s="49" customFormat="1" spans="1:13">
+    <row r="21" s="49" customFormat="1" spans="1:14">
       <c r="A21" s="58"/>
       <c r="B21" s="49" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="C21" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12214,10 +12904,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" s="49" customFormat="1" spans="1:13">
+    <row r="22" s="49" customFormat="1" spans="1:14">
       <c r="A22" s="58"/>
       <c r="B22" s="49" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="C22" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12251,10 +12941,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" s="49" customFormat="1" spans="1:13">
+    <row r="23" s="49" customFormat="1" spans="1:14">
       <c r="A23" s="58"/>
       <c r="B23" s="49" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="C23" s="49" t="b">
         <f t="shared" si="1"/>
@@ -12291,7 +12981,7 @@
     <row r="24" s="51" customFormat="1" spans="1:14">
       <c r="A24" s="58"/>
       <c r="B24" s="59" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="C24" s="59" t="b">
         <f>FALSE()</f>
@@ -12329,19 +13019,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" s="52" customFormat="1" spans="1:12">
+    <row r="25" s="52" customFormat="1" spans="1:14">
       <c r="A25" s="60" t="s">
         <v>329</v>
       </c>
       <c r="B25" s="52" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="C25" s="52" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="G25" s="52">
         <v>1</v>
@@ -12362,17 +13052,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="52" customFormat="1" spans="1:12">
+    <row r="26" s="52" customFormat="1" spans="1:14">
       <c r="A26" s="60"/>
       <c r="B26" s="52" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="C26" s="52" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="G26" s="52">
         <v>1</v>
@@ -12393,19 +13083,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="49" customFormat="1" spans="1:12">
+    <row r="27" s="49" customFormat="1" spans="1:14">
       <c r="A27" s="58" t="s">
         <v>338</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="C27" s="49" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="E27" s="49">
         <v>33</v>
@@ -12432,17 +13122,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="49" customFormat="1" spans="1:12">
+    <row r="28" s="49" customFormat="1" spans="1:14">
       <c r="A28" s="58"/>
       <c r="B28" s="49" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="C28" s="49" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="G28" s="49">
         <v>1</v>
@@ -12466,14 +13156,14 @@
     <row r="29" s="49" customFormat="1" spans="1:14">
       <c r="A29" s="58"/>
       <c r="B29" s="49" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="C29" s="49" t="b">
         <f t="shared" ref="C29:C34" si="2">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="E29" s="49">
         <v>66</v>
@@ -12509,14 +13199,14 @@
     <row r="30" s="49" customFormat="1" spans="1:14">
       <c r="A30" s="58"/>
       <c r="B30" s="49" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="C30" s="49" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="E30" s="49">
         <v>0</v>
@@ -12549,17 +13239,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" s="49" customFormat="1" spans="1:12">
+    <row r="31" s="49" customFormat="1" spans="1:14">
       <c r="A31" s="58"/>
       <c r="B31" s="49" t="s">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="C31" s="49" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="E31" s="49">
         <v>66</v>
@@ -12586,17 +13276,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" s="49" customFormat="1" spans="1:12">
+    <row r="32" s="49" customFormat="1" spans="1:14">
       <c r="A32" s="58"/>
       <c r="B32" s="49" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="C32" s="49" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="E32" s="49">
         <v>33</v>
@@ -12623,17 +13313,17 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" s="49" customFormat="1" spans="1:12">
+    <row r="33" s="49" customFormat="1" spans="1:14">
       <c r="A33" s="58"/>
       <c r="B33" s="49" t="s">
-        <v>655</v>
+        <v>687</v>
       </c>
       <c r="C33" s="49" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="E33" s="49">
         <v>0</v>
@@ -12665,14 +13355,14 @@
         <v>348</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="C34" s="47" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="G34" s="47">
         <v>1</v>
@@ -12699,17 +13389,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="35" s="47" customFormat="1" spans="1:12">
+    <row r="35" s="47" customFormat="1" spans="1:14">
       <c r="A35" s="61"/>
       <c r="B35" s="47" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="C35" s="47" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="G35" s="47">
         <v>1</v>
@@ -12730,19 +13420,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" s="46" customFormat="1" spans="1:12">
+    <row r="36" s="46" customFormat="1" spans="1:14">
       <c r="A36" s="46" t="s">
         <v>372</v>
       </c>
       <c r="B36" s="46" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="C36" s="46" t="b">
         <f t="shared" ref="C36:C50" si="3">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="G36" s="46">
         <v>1</v>
@@ -12763,19 +13453,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" s="53" customFormat="1" spans="1:12">
+    <row r="37" s="53" customFormat="1" spans="1:14">
       <c r="A37" s="53" t="s">
         <v>375</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="C37" s="53" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="G37" s="53">
         <v>1</v>
@@ -12796,19 +13486,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" s="48" customFormat="1" spans="1:12">
+    <row r="38" s="48" customFormat="1" spans="1:14">
       <c r="A38" s="48" t="s">
         <v>378</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="C38" s="48" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="G38" s="48">
         <v>1</v>
@@ -12829,19 +13519,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" s="49" customFormat="1" spans="1:12">
+    <row r="39" s="49" customFormat="1" spans="1:14">
       <c r="A39" s="58" t="s">
         <v>381</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="C39" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="E39" s="49">
         <v>66</v>
@@ -12868,17 +13558,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" s="49" customFormat="1" spans="1:13">
+    <row r="40" s="49" customFormat="1" spans="1:14">
       <c r="A40" s="58"/>
       <c r="B40" s="49" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="C40" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="E40" s="49">
         <v>33</v>
@@ -12908,17 +13598,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" s="49" customFormat="1" spans="1:13">
+    <row r="41" s="49" customFormat="1" spans="1:14">
       <c r="A41" s="58"/>
       <c r="B41" s="49" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="C41" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="E41" s="49">
         <v>0</v>
@@ -12948,17 +13638,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" s="49" customFormat="1" spans="1:12">
+    <row r="42" s="49" customFormat="1" spans="1:14">
       <c r="A42" s="58"/>
       <c r="B42" s="49" t="s">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="C42" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="E42" s="49">
         <v>66</v>
@@ -12985,17 +13675,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" s="49" customFormat="1" spans="1:12">
+    <row r="43" s="49" customFormat="1" spans="1:14">
       <c r="A43" s="58"/>
       <c r="B43" s="49" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="C43" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="E43" s="49">
         <v>33</v>
@@ -13022,17 +13712,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" s="49" customFormat="1" spans="1:12">
+    <row r="44" s="49" customFormat="1" spans="1:14">
       <c r="A44" s="58"/>
       <c r="B44" s="49" t="s">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="C44" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="E44" s="49">
         <v>0</v>
@@ -13059,17 +13749,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" s="49" customFormat="1" spans="1:12">
+    <row r="45" s="49" customFormat="1" spans="1:14">
       <c r="A45" s="58"/>
       <c r="B45" s="49" t="s">
-        <v>672</v>
+        <v>704</v>
       </c>
       <c r="C45" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="E45" s="49">
         <v>66</v>
@@ -13096,17 +13786,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" s="49" customFormat="1" spans="1:12">
+    <row r="46" s="49" customFormat="1" spans="1:14">
       <c r="A46" s="58"/>
       <c r="B46" s="49" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="C46" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="E46" s="49">
         <v>33</v>
@@ -13133,17 +13823,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" s="49" customFormat="1" spans="1:12">
+    <row r="47" s="49" customFormat="1" spans="1:14">
       <c r="A47" s="58"/>
       <c r="B47" s="49" t="s">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="C47" s="49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="E47" s="49">
         <v>0</v>
@@ -13170,19 +13860,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:14">
       <c r="A48" s="15" t="s">
         <v>396</v>
       </c>
       <c r="B48" t="s">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="C48" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -13203,19 +13893,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:14">
       <c r="A49" s="15" t="s">
         <v>399</v>
       </c>
       <c r="B49" t="s">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="C49" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -13236,19 +13926,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:14">
       <c r="A50" s="15" t="s">
         <v>402</v>
       </c>
       <c r="B50" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="C50" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -13269,19 +13959,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" s="46" customFormat="1" spans="1:12">
+    <row r="51" s="46" customFormat="1" spans="1:14">
       <c r="A51" s="62" t="s">
         <v>384</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="C51" s="46" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="G51" s="46">
         <v>1</v>
@@ -13305,14 +13995,14 @@
     <row r="52" s="46" customFormat="1" spans="1:14">
       <c r="A52" s="62"/>
       <c r="B52" s="46" t="s">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="C52" s="46" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="G52" s="46">
         <v>1</v>
@@ -13339,19 +14029,19 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="53" s="48" customFormat="1" spans="1:12">
+    <row r="53" s="48" customFormat="1" spans="1:14">
       <c r="A53" s="63" t="s">
         <v>387</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="C53" s="48" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="G53" s="48">
         <v>1</v>
@@ -13372,17 +14062,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" s="48" customFormat="1" spans="1:12">
+    <row r="54" s="48" customFormat="1" spans="1:14">
       <c r="A54" s="63"/>
       <c r="B54" s="48" t="s">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="C54" s="48" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="G54" s="48">
         <v>1</v>
@@ -13403,19 +14093,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" s="47" customFormat="1" spans="1:12">
+    <row r="55" s="47" customFormat="1" spans="1:14">
       <c r="A55" s="64" t="s">
         <v>390</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="C55" s="47" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="G55" s="47">
         <v>1</v>
@@ -13439,14 +14129,14 @@
     <row r="56" s="47" customFormat="1" spans="1:14">
       <c r="A56" s="64"/>
       <c r="B56" s="47" t="s">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="C56" s="47" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="G56" s="47">
         <v>1</v>
@@ -13470,19 +14160,19 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="57" s="54" customFormat="1" spans="1:12">
+    <row r="57" s="54" customFormat="1" spans="1:14">
       <c r="A57" s="65" t="s">
         <v>393</v>
       </c>
       <c r="B57" s="54" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="C57" s="54" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="G57" s="54">
         <v>1</v>
@@ -13503,14 +14193,14 @@
     <row r="58" s="54" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A58" s="65"/>
       <c r="B58" s="54" t="s">
-        <v>688</v>
+        <v>720</v>
       </c>
       <c r="C58" s="54" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D58" s="54" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="E58" s="54">
         <v>66</v>
@@ -13546,14 +14236,14 @@
     <row r="59" s="54" customFormat="1" spans="1:14">
       <c r="A59" s="65"/>
       <c r="B59" s="54" t="s">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="C59" s="54" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D59" s="54" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="E59" s="54">
         <v>33</v>
@@ -13589,14 +14279,14 @@
     <row r="60" s="54" customFormat="1" spans="1:14">
       <c r="A60" s="65"/>
       <c r="B60" s="54" t="s">
-        <v>691</v>
+        <v>723</v>
       </c>
       <c r="C60" s="54" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D60" s="54" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="E60" s="54">
         <v>0</v>
@@ -13629,17 +14319,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" s="54" customFormat="1" spans="1:12">
+    <row r="61" s="54" customFormat="1" spans="1:14">
       <c r="A61" s="65"/>
       <c r="B61" s="54" t="s">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="C61" s="54" t="b">
         <f t="shared" ref="C61:C68" si="4">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D61" s="54" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="E61" s="54">
         <v>66</v>
@@ -13666,17 +14356,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" s="54" customFormat="1" spans="1:13">
+    <row r="62" s="54" customFormat="1" spans="1:14">
       <c r="A62" s="65"/>
       <c r="B62" s="54" t="s">
-        <v>693</v>
+        <v>725</v>
       </c>
       <c r="C62" s="54" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D62" s="54" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="E62" s="54">
         <v>33</v>
@@ -13706,17 +14396,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" s="54" customFormat="1" spans="1:13">
+    <row r="63" s="54" customFormat="1" spans="1:14">
       <c r="A63" s="65"/>
       <c r="B63" s="54" t="s">
-        <v>694</v>
+        <v>726</v>
       </c>
       <c r="C63" s="54" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D63" s="54" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="E63" s="54">
         <v>0</v>
@@ -13749,14 +14439,14 @@
     <row r="64" s="54" customFormat="1" spans="1:14">
       <c r="A64" s="65"/>
       <c r="B64" s="54" t="s">
-        <v>695</v>
+        <v>727</v>
       </c>
       <c r="C64" s="54" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D64" s="54" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="E64" s="54">
         <v>66</v>
@@ -13789,14 +14479,14 @@
     <row r="65" s="54" customFormat="1" spans="1:14">
       <c r="A65" s="65"/>
       <c r="B65" s="54" t="s">
-        <v>696</v>
+        <v>728</v>
       </c>
       <c r="C65" s="54" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D65" s="54" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="E65" s="54">
         <v>33</v>
@@ -13829,14 +14519,14 @@
     <row r="66" s="54" customFormat="1" spans="1:14">
       <c r="A66" s="65"/>
       <c r="B66" s="54" t="s">
-        <v>697</v>
+        <v>729</v>
       </c>
       <c r="C66" s="54" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D66" s="54" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="E66" s="54">
         <v>0</v>
@@ -13866,19 +14556,19 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="67" s="55" customFormat="1" spans="1:12">
+    <row r="67" s="55" customFormat="1" spans="1:14">
       <c r="A67" s="66" t="s">
         <v>405</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="C67" s="55" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="E67" s="55">
         <v>50</v>
@@ -13905,17 +14595,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" s="55" customFormat="1" spans="1:12">
+    <row r="68" s="55" customFormat="1" spans="1:14">
       <c r="A68" s="66"/>
       <c r="B68" s="55" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="C68" s="55" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="E68" s="55">
         <v>0</v>
@@ -13942,19 +14632,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" s="56" customFormat="1" spans="1:12">
+    <row r="69" s="56" customFormat="1" spans="1:14">
       <c r="A69" s="67" t="s">
         <v>408</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="C69" s="56" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D69" s="56" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="G69" s="56">
         <v>1</v>
@@ -13975,17 +14665,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" s="56" customFormat="1" spans="1:12">
+    <row r="70" s="56" customFormat="1" spans="1:14">
       <c r="A70" s="67"/>
       <c r="B70" s="56" t="s">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="C70" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D70" s="56" t="s">
-        <v>701</v>
+        <v>733</v>
       </c>
       <c r="E70" s="56">
         <v>50</v>
@@ -14012,17 +14702,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" s="56" customFormat="1" spans="1:13">
+    <row r="71" s="56" customFormat="1" spans="1:14">
       <c r="A71" s="67"/>
       <c r="B71" s="56" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="C71" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D71" s="56" t="s">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="E71" s="56">
         <v>0</v>
@@ -14052,19 +14742,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" s="57" customFormat="1" spans="1:12">
+    <row r="72" s="57" customFormat="1" spans="1:14">
       <c r="A72" s="68" t="s">
         <v>411</v>
       </c>
       <c r="B72" s="57" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="C72" s="56" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D72" s="57" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="G72" s="57">
         <v>1</v>
@@ -14085,17 +14775,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" s="57" customFormat="1" spans="1:13">
+    <row r="73" s="57" customFormat="1" spans="1:14">
       <c r="A73" s="68"/>
       <c r="B73" s="57" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="C73" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D73" s="57" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="E73" s="57">
         <v>66</v>
@@ -14125,17 +14815,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" s="57" customFormat="1" spans="1:13">
+    <row r="74" s="57" customFormat="1" spans="1:14">
       <c r="A74" s="68"/>
       <c r="B74" s="57" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="C74" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D74" s="57" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="E74" s="57">
         <v>33</v>
@@ -14165,17 +14855,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" s="57" customFormat="1" spans="1:12">
+    <row r="75" s="57" customFormat="1" spans="1:14">
       <c r="A75" s="68"/>
       <c r="B75" s="57" t="s">
-        <v>708</v>
+        <v>740</v>
       </c>
       <c r="C75" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D75" s="57" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="E75" s="57">
         <v>33</v>
@@ -14202,17 +14892,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" s="57" customFormat="1" spans="1:13">
+    <row r="76" s="57" customFormat="1" spans="1:14">
       <c r="A76" s="68"/>
       <c r="B76" s="57" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="C76" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D76" s="57" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="E76" s="57">
         <v>0</v>
@@ -14242,19 +14932,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" s="57" customFormat="1" spans="1:12">
+    <row r="77" s="57" customFormat="1" spans="1:14">
       <c r="A77" s="68" t="s">
         <v>414</v>
       </c>
       <c r="B77" s="57" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="C77" s="56" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D77" s="57" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="G77" s="57">
         <v>1</v>
@@ -14275,17 +14965,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" s="57" customFormat="1" spans="1:12">
+    <row r="78" s="57" customFormat="1" spans="1:14">
       <c r="A78" s="68"/>
       <c r="B78" s="57" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="C78" s="57" t="b">
         <f t="shared" ref="C78:C86" si="5">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D78" s="57" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="E78" s="57">
         <v>66</v>
@@ -14312,17 +15002,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" s="57" customFormat="1" spans="1:12">
+    <row r="79" s="57" customFormat="1" spans="1:14">
       <c r="A79" s="68"/>
       <c r="B79" s="57" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="C79" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D79" s="57" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="E79" s="57">
         <v>33</v>
@@ -14349,17 +15039,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" s="57" customFormat="1" spans="1:12">
+    <row r="80" s="57" customFormat="1" spans="1:14">
       <c r="A80" s="68"/>
       <c r="B80" s="57" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="C80" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D80" s="57" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="E80" s="57">
         <v>0</v>
@@ -14386,17 +15076,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" s="57" customFormat="1" spans="1:12">
+    <row r="81" s="57" customFormat="1" spans="1:13">
       <c r="A81" s="68"/>
       <c r="B81" s="57" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="C81" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D81" s="57" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="E81" s="57">
         <v>66</v>
@@ -14423,17 +15113,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" s="57" customFormat="1" spans="1:12">
+    <row r="82" s="57" customFormat="1" spans="1:13">
       <c r="A82" s="68"/>
       <c r="B82" s="57" t="s">
-        <v>714</v>
+        <v>746</v>
       </c>
       <c r="C82" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D82" s="57" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="E82" s="57">
         <v>33</v>
@@ -14460,17 +15150,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" s="57" customFormat="1" spans="1:12">
+    <row r="83" s="57" customFormat="1" spans="1:13">
       <c r="A83" s="68"/>
       <c r="B83" s="57" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="C83" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D83" s="57" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="E83" s="57">
         <v>0</v>
@@ -14500,14 +15190,14 @@
     <row r="84" s="57" customFormat="1" spans="1:13">
       <c r="A84" s="68"/>
       <c r="B84" s="57" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="C84" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D84" s="57" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="E84" s="57">
         <v>66</v>
@@ -14540,14 +15230,14 @@
     <row r="85" s="57" customFormat="1" spans="1:13">
       <c r="A85" s="68"/>
       <c r="B85" s="57" t="s">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="C85" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D85" s="57" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="E85" s="57">
         <v>33</v>
@@ -14580,14 +15270,14 @@
     <row r="86" s="57" customFormat="1" spans="1:13">
       <c r="A86" s="68"/>
       <c r="B86" s="57" t="s">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="C86" s="57" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D86" s="57" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="E86" s="57">
         <v>0</v>
@@ -14617,19 +15307,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" spans="1:12">
+    <row r="87" s="1" customFormat="1" spans="1:13">
       <c r="A87" s="69" t="s">
         <v>417</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="C87" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -14650,17 +15340,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" spans="1:12">
+    <row r="88" s="1" customFormat="1" spans="1:13">
       <c r="A88" s="69"/>
       <c r="B88" s="1" t="s">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="C88" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -14681,19 +15371,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:13">
       <c r="A89" s="70" t="s">
         <v>420</v>
       </c>
       <c r="B89" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="C89" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -14717,14 +15407,14 @@
     <row r="90" spans="1:13">
       <c r="A90" s="70"/>
       <c r="B90" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="C90" t="b">
         <f t="shared" ref="C90:C96" si="6">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="E90">
         <v>66</v>
@@ -14757,14 +15447,14 @@
     <row r="91" spans="1:13">
       <c r="A91" s="70"/>
       <c r="B91" t="s">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="C91" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="E91">
         <v>33</v>
@@ -14797,14 +15487,14 @@
     <row r="92" spans="1:13">
       <c r="A92" s="70"/>
       <c r="B92" t="s">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="C92" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14837,14 +15527,14 @@
     <row r="93" spans="1:13">
       <c r="A93" s="70"/>
       <c r="B93" t="s">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="C93" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="E93">
         <v>66</v>
@@ -14877,14 +15567,14 @@
     <row r="94" spans="1:13">
       <c r="A94" s="70"/>
       <c r="B94" t="s">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="C94" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="E94">
         <v>33</v>
@@ -14917,14 +15607,14 @@
     <row r="95" spans="1:13">
       <c r="A95" s="70"/>
       <c r="B95" t="s">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="C95" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14954,19 +15644,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" s="55" customFormat="1" spans="1:12">
+    <row r="96" s="55" customFormat="1" spans="1:13">
       <c r="A96" s="66" t="s">
         <v>423</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="C96" s="55" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="G96" s="55">
         <v>1</v>
@@ -14987,19 +15677,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" s="56" customFormat="1" spans="1:12">
+    <row r="97" s="56" customFormat="1" spans="1:13">
       <c r="A97" s="67" t="s">
         <v>426</v>
       </c>
       <c r="B97" s="56" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="C97" s="56" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D97" s="56" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="G97" s="56">
         <v>1</v>
@@ -15023,14 +15713,14 @@
     <row r="98" s="56" customFormat="1" spans="1:13">
       <c r="A98" s="67"/>
       <c r="B98" s="56" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="C98" s="56" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="D98" s="56" t="s">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="G98" s="56">
         <v>1</v>
@@ -15081,7 +15771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E90"/>
@@ -15097,19 +15787,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="24" t="s">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15120,7 +15810,7 @@
         <v>350</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
@@ -15138,7 +15828,7 @@
         <v>350</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="D3" s="24">
         <v>1</v>
@@ -15156,7 +15846,7 @@
         <v>294</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="D4" s="24">
         <v>1</v>
@@ -15174,7 +15864,7 @@
         <v>294</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="D5" s="24">
         <v>1</v>
@@ -15192,7 +15882,7 @@
         <v>294</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="D6" s="30">
         <v>1</v>
@@ -15210,7 +15900,7 @@
         <v>294</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="D7" s="30">
         <v>1</v>
@@ -15228,7 +15918,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="D8" s="30">
         <v>1</v>
@@ -15246,7 +15936,7 @@
         <v>350</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>741</v>
+        <v>773</v>
       </c>
       <c r="D9" s="30">
         <v>1</v>
@@ -15264,7 +15954,7 @@
         <v>320</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="D10" s="24">
         <v>1</v>
@@ -15282,7 +15972,7 @@
         <v>320</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>743</v>
+        <v>775</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
@@ -15300,7 +15990,7 @@
         <v>294</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="D12" s="24">
         <v>1</v>
@@ -15318,7 +16008,7 @@
         <v>294</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>745</v>
+        <v>777</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
@@ -15336,7 +16026,7 @@
         <v>350</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="D14" s="24">
         <v>1</v>
@@ -15354,7 +16044,7 @@
         <v>350</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>747</v>
+        <v>779</v>
       </c>
       <c r="D15" s="24">
         <v>1</v>
@@ -15372,7 +16062,7 @@
         <v>320</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>748</v>
+        <v>780</v>
       </c>
       <c r="D16" s="24">
         <v>1</v>
@@ -15390,7 +16080,7 @@
         <v>320</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>749</v>
+        <v>781</v>
       </c>
       <c r="D17" s="24">
         <v>1</v>
@@ -15408,7 +16098,7 @@
         <v>340</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="D18" s="30">
         <v>-1</v>
@@ -15426,7 +16116,7 @@
         <v>340</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>751</v>
+        <v>783</v>
       </c>
       <c r="D19" s="30">
         <v>-1</v>
@@ -15444,7 +16134,7 @@
         <v>340</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
       <c r="D20" s="30">
         <v>1</v>
@@ -15462,7 +16152,7 @@
         <v>340</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="D21" s="30">
         <v>1</v>
@@ -15480,7 +16170,7 @@
         <v>340</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>754</v>
+        <v>786</v>
       </c>
       <c r="D22" s="30">
         <v>1</v>
@@ -15498,7 +16188,7 @@
         <v>340</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="D23" s="30">
         <v>1</v>
@@ -15516,7 +16206,7 @@
         <v>320</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="D24" s="24">
         <v>1</v>
@@ -15534,7 +16224,7 @@
         <v>320</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>757</v>
+        <v>789</v>
       </c>
       <c r="D25" s="24">
         <v>1</v>
@@ -15552,7 +16242,7 @@
         <v>331</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>758</v>
+        <v>790</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
@@ -15570,7 +16260,7 @@
         <v>294</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="D27" s="24">
         <v>1</v>
@@ -15588,7 +16278,7 @@
         <v>294</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>760</v>
+        <v>792</v>
       </c>
       <c r="D28" s="24">
         <v>1</v>
@@ -15606,7 +16296,7 @@
         <v>350</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="D29" s="38">
         <v>1</v>
@@ -15624,7 +16314,7 @@
         <v>350</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>762</v>
+        <v>794</v>
       </c>
       <c r="D30" s="24">
         <v>1</v>
@@ -15642,7 +16332,7 @@
         <v>320</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>763</v>
+        <v>795</v>
       </c>
       <c r="D31" s="24">
         <v>1</v>
@@ -15660,7 +16350,7 @@
         <v>320</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>764</v>
+        <v>796</v>
       </c>
       <c r="D32" s="24">
         <v>1</v>
@@ -15678,7 +16368,7 @@
         <v>350</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
       <c r="D33" s="24">
         <v>1</v>
@@ -15696,7 +16386,7 @@
         <v>340</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>766</v>
+        <v>798</v>
       </c>
       <c r="D34" s="30">
         <v>1</v>
@@ -15712,7 +16402,7 @@
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="25" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="D35" s="24">
         <v>1</v>
@@ -15730,7 +16420,7 @@
         <v>350</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="D36" s="24">
         <v>1</v>
@@ -15746,7 +16436,7 @@
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="25" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
       <c r="D37" s="24">
         <v>1</v>
@@ -15764,7 +16454,7 @@
         <v>308</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="D38" s="24">
         <v>1</v>
@@ -15782,7 +16472,7 @@
         <v>308</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>771</v>
+        <v>803</v>
       </c>
       <c r="D39" s="24">
         <v>1</v>
@@ -15798,7 +16488,7 @@
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="38" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="D40" s="24">
         <v>1</v>
@@ -15816,7 +16506,7 @@
         <v>350</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>773</v>
+        <v>805</v>
       </c>
       <c r="D41" s="24">
         <v>-1</v>
@@ -15832,7 +16522,7 @@
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="25" t="s">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="D42" s="24">
         <v>1</v>
@@ -15848,7 +16538,7 @@
       </c>
       <c r="B43" s="24"/>
       <c r="C43" s="25" t="s">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="D43" s="24">
         <v>1</v>
@@ -15866,7 +16556,7 @@
         <v>331</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>776</v>
+        <v>808</v>
       </c>
       <c r="D44" s="24">
         <v>1</v>
@@ -15882,7 +16572,7 @@
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="38" t="s">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="D45" s="24">
         <v>1</v>
@@ -15900,7 +16590,7 @@
         <v>331</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>778</v>
+        <v>810</v>
       </c>
       <c r="D46" s="24">
         <v>1</v>
@@ -15918,7 +16608,7 @@
         <v>350</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="D47" s="24">
         <v>1</v>
@@ -15934,7 +16624,7 @@
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="41" t="s">
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="D48" s="24">
         <v>1</v>
@@ -15952,7 +16642,7 @@
         <v>294</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>781</v>
+        <v>813</v>
       </c>
       <c r="D49" s="24">
         <v>1</v>
@@ -15970,7 +16660,7 @@
         <v>294</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>782</v>
+        <v>814</v>
       </c>
       <c r="D50" s="24">
         <v>1</v>
@@ -15988,7 +16678,7 @@
         <v>308</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>783</v>
+        <v>815</v>
       </c>
       <c r="D51" s="24">
         <v>1</v>
@@ -16006,7 +16696,7 @@
         <v>331</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="D52" s="24">
         <v>1</v>
@@ -16024,7 +16714,7 @@
         <v>331</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="D53" s="24">
         <v>1</v>
@@ -16040,7 +16730,7 @@
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="25" t="s">
-        <v>786</v>
+        <v>818</v>
       </c>
       <c r="D54" s="24">
         <v>1</v>
@@ -16058,7 +16748,7 @@
         <v>340</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>787</v>
+        <v>819</v>
       </c>
       <c r="D55" s="30">
         <v>1</v>
@@ -16076,7 +16766,7 @@
         <v>308</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="D56" s="24">
         <v>1</v>
@@ -16092,7 +16782,7 @@
       </c>
       <c r="B57" s="24"/>
       <c r="C57" s="25" t="s">
-        <v>789</v>
+        <v>821</v>
       </c>
       <c r="D57" s="24">
         <v>1</v>
@@ -16108,7 +16798,7 @@
       </c>
       <c r="B58" s="24"/>
       <c r="C58" s="25" t="s">
-        <v>790</v>
+        <v>822</v>
       </c>
       <c r="D58" s="24">
         <v>1</v>
@@ -16126,7 +16816,7 @@
         <v>340</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>791</v>
+        <v>823</v>
       </c>
       <c r="D59" s="30">
         <v>1</v>
@@ -16144,7 +16834,7 @@
         <v>340</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="D60" s="30">
         <v>1</v>
@@ -16162,7 +16852,7 @@
         <v>340</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="D61" s="30">
         <v>1</v>
@@ -16180,7 +16870,7 @@
         <v>350</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="D62" s="24">
         <v>1</v>
@@ -16196,7 +16886,7 @@
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="25" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="D63" s="24">
         <v>1</v>
@@ -16212,7 +16902,7 @@
       </c>
       <c r="B64" s="24"/>
       <c r="C64" s="43" t="s">
-        <v>796</v>
+        <v>828</v>
       </c>
       <c r="D64" s="24">
         <v>1</v>
@@ -16228,7 +16918,7 @@
       </c>
       <c r="B65" s="24"/>
       <c r="C65" s="43" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="D65" s="24">
         <v>1</v>
@@ -16246,7 +16936,7 @@
         <v>294</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="D66" s="24">
         <v>1</v>
@@ -16264,7 +16954,7 @@
         <v>294</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="D67" s="24">
         <v>1</v>
@@ -16282,7 +16972,7 @@
         <v>294</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="D68" s="24">
         <v>1</v>
@@ -16300,7 +16990,7 @@
         <v>294</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="D69" s="24">
         <v>1</v>
@@ -16318,7 +17008,7 @@
         <v>350</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="D70" s="24">
         <v>1</v>
@@ -16336,7 +17026,7 @@
         <v>350</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>803</v>
+        <v>835</v>
       </c>
       <c r="D71" s="24">
         <v>1</v>
@@ -16354,7 +17044,7 @@
         <v>350</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>804</v>
+        <v>836</v>
       </c>
       <c r="D72" s="24">
         <v>1</v>
@@ -16372,7 +17062,7 @@
         <v>350</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>805</v>
+        <v>837</v>
       </c>
       <c r="D73" s="24">
         <v>1</v>
@@ -16390,7 +17080,7 @@
         <v>294</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>806</v>
+        <v>838</v>
       </c>
       <c r="D74" s="24">
         <v>1</v>
@@ -16408,7 +17098,7 @@
         <v>350</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>807</v>
+        <v>839</v>
       </c>
       <c r="D75" s="24">
         <v>-1</v>
@@ -16426,7 +17116,7 @@
         <v>340</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>808</v>
+        <v>840</v>
       </c>
       <c r="D76" s="24">
         <v>1</v>
@@ -16444,7 +17134,7 @@
         <v>340</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>809</v>
+        <v>841</v>
       </c>
       <c r="D77" s="24">
         <v>1</v>
@@ -16462,7 +17152,7 @@
         <v>340</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>810</v>
+        <v>842</v>
       </c>
       <c r="D78" s="24">
         <v>1</v>
@@ -16480,7 +17170,7 @@
         <v>340</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>811</v>
+        <v>843</v>
       </c>
       <c r="D79" s="24">
         <v>1</v>
@@ -16496,7 +17186,7 @@
       </c>
       <c r="B80" s="24"/>
       <c r="C80" s="39" t="s">
-        <v>812</v>
+        <v>844</v>
       </c>
       <c r="D80" s="24">
         <v>1</v>
@@ -16511,7 +17201,7 @@
       </c>
       <c r="B81" s="24"/>
       <c r="C81" s="24" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="D81" s="24">
         <v>1</v>
@@ -16526,7 +17216,7 @@
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="24" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="D82" s="24">
         <v>1</v>
@@ -16541,7 +17231,7 @@
       </c>
       <c r="B83" s="24"/>
       <c r="C83" s="24" t="s">
-        <v>815</v>
+        <v>847</v>
       </c>
       <c r="D83" s="24">
         <v>1</v>
@@ -16556,7 +17246,7 @@
       </c>
       <c r="B84" s="24"/>
       <c r="C84" s="24" t="s">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="D84" s="24">
         <v>1</v>
@@ -16571,7 +17261,7 @@
       </c>
       <c r="B85" s="24"/>
       <c r="C85" s="24" t="s">
-        <v>817</v>
+        <v>849</v>
       </c>
       <c r="D85" s="24">
         <v>1</v>
@@ -16586,7 +17276,7 @@
       </c>
       <c r="B86" s="24"/>
       <c r="C86" s="24" t="s">
-        <v>818</v>
+        <v>850</v>
       </c>
       <c r="D86" s="24">
         <v>1</v>
@@ -16601,7 +17291,7 @@
       </c>
       <c r="B87" s="24"/>
       <c r="C87" s="24" t="s">
-        <v>819</v>
+        <v>851</v>
       </c>
       <c r="D87" s="24">
         <v>1</v>
@@ -16618,7 +17308,7 @@
         <v>331</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>820</v>
+        <v>852</v>
       </c>
       <c r="D88" s="24">
         <v>1</v>
@@ -16633,7 +17323,7 @@
       </c>
       <c r="B89" s="24"/>
       <c r="C89" s="25" t="s">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="D89" s="24">
         <v>1</v>
@@ -16648,7 +17338,7 @@
       </c>
       <c r="B90" s="24"/>
       <c r="C90" s="25" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="D90" s="24">
         <v>1</v>
@@ -16665,7 +17355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AK7"/>
@@ -16709,122 +17399,122 @@
     <col min="36" max="1025" width="9.14285714285714" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:37">
       <c r="A1" s="16" t="s">
         <v>250</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>823</v>
+        <v>855</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>825</v>
+        <v>857</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>827</v>
+        <v>859</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>828</v>
+        <v>860</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>829</v>
+        <v>861</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>830</v>
+        <v>862</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>832</v>
+        <v>864</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>833</v>
+        <v>865</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>834</v>
+        <v>866</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>836</v>
+        <v>868</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>838</v>
+        <v>870</v>
       </c>
       <c r="U1" s="16" t="s">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="V1" s="16" t="s">
-        <v>840</v>
+        <v>872</v>
       </c>
       <c r="W1" s="16" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="X1" s="16" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="Y1" s="16" t="s">
-        <v>843</v>
+        <v>875</v>
       </c>
       <c r="Z1" s="16" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
       <c r="AA1" s="16" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="AB1" s="16" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
       <c r="AC1" s="16" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="AD1" s="16" t="s">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="AE1" s="16" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="AF1" s="16" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="AG1" s="16" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="AH1" s="16" t="s">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="AI1" s="16" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="2" s="13" customFormat="1" spans="1:35">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="2" s="13" customFormat="1" spans="1:37">
       <c r="A2" s="17">
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="D2" s="17" t="b">
         <f t="shared" ref="D2:D7" si="0">TRUE()</f>
@@ -16865,10 +17555,10 @@
       <c r="Q2" s="17">
         <v>14</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="S2" s="20">
+      <c r="S2" s="18">
         <v>1.5</v>
       </c>
       <c r="T2" s="17" t="s">
@@ -16877,16 +17567,16 @@
       <c r="U2" s="17">
         <v>8</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="W2" s="20">
+      <c r="W2" s="18">
         <v>32</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="X2" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="Y2" s="20">
+      <c r="Y2" s="18">
         <v>0</v>
       </c>
       <c r="Z2" s="17" t="s">
@@ -16914,15 +17604,15 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="3" s="13" customFormat="1" spans="1:36">
+    <row r="3" s="13" customFormat="1" spans="1:37">
       <c r="A3" s="17">
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="D3" s="17" t="b">
         <f t="shared" si="0"/>
@@ -16963,10 +17653,10 @@
       <c r="Q3" s="17">
         <v>10</v>
       </c>
-      <c r="R3" s="20" t="s">
+      <c r="R3" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="18">
         <v>1.5</v>
       </c>
       <c r="T3" s="17" t="s">
@@ -16975,16 +17665,16 @@
       <c r="U3" s="17">
         <v>8</v>
       </c>
-      <c r="V3" s="20" t="s">
+      <c r="V3" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="W3" s="20">
+      <c r="W3" s="18">
         <v>6</v>
       </c>
-      <c r="X3" s="20" t="s">
+      <c r="X3" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="Y3" s="20">
+      <c r="Y3" s="18">
         <v>0</v>
       </c>
       <c r="Z3" s="17" t="s">
@@ -17024,10 +17714,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>857</v>
+        <v>889</v>
       </c>
       <c r="D4" s="17" t="b">
         <f t="shared" si="0"/>
@@ -17068,10 +17758,10 @@
       <c r="Q4" s="17">
         <v>18</v>
       </c>
-      <c r="R4" s="20" t="s">
+      <c r="R4" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="S4" s="20">
+      <c r="S4" s="18">
         <v>4</v>
       </c>
       <c r="T4" s="17" t="s">
@@ -17080,16 +17770,16 @@
       <c r="U4" s="17">
         <v>31</v>
       </c>
-      <c r="V4" s="20" t="s">
+      <c r="V4" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="W4" s="20">
+      <c r="W4" s="18">
         <v>2</v>
       </c>
-      <c r="X4" s="20" t="s">
+      <c r="X4" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="Y4" s="20">
+      <c r="Y4" s="18">
         <v>0</v>
       </c>
       <c r="Z4" s="17" t="s">
@@ -17124,15 +17814,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" s="13" customFormat="1" spans="1:35">
+    <row r="5" s="13" customFormat="1" spans="1:37">
       <c r="A5" s="17">
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>859</v>
+        <v>891</v>
       </c>
       <c r="D5" s="17" t="b">
         <f t="shared" si="0"/>
@@ -17173,10 +17863,10 @@
       <c r="Q5" s="17">
         <v>14</v>
       </c>
-      <c r="R5" s="20" t="s">
+      <c r="R5" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="18">
         <v>2</v>
       </c>
       <c r="T5" s="17" t="s">
@@ -17185,16 +17875,16 @@
       <c r="U5" s="17">
         <v>15</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="W5" s="20">
+      <c r="W5" s="18">
         <v>8</v>
       </c>
-      <c r="X5" s="20" t="s">
+      <c r="X5" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="Y5" s="20">
+      <c r="Y5" s="18">
         <v>1.8</v>
       </c>
       <c r="Z5" s="17" t="s">
@@ -17224,204 +17914,204 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="6" s="14" customFormat="1" spans="1:35">
-      <c r="A6" s="18">
+    <row r="6" s="14" customFormat="1" spans="1:37">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>860</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="D6" s="19" t="b">
+      <c r="B6" s="20" t="s">
+        <v>892</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>893</v>
+      </c>
+      <c r="D6" s="20" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19">
+      <c r="G6" s="20"/>
+      <c r="H6" s="20">
         <v>9</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <v>300</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <v>3.3</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="20">
         <v>0.8</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="20">
         <v>2</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="P6" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="20">
         <v>16</v>
       </c>
-      <c r="R6" s="19" t="s">
+      <c r="R6" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="20">
         <v>4</v>
       </c>
-      <c r="T6" s="19" t="s">
+      <c r="T6" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="U6" s="19">
+      <c r="U6" s="20">
         <v>30</v>
       </c>
-      <c r="V6" s="19" t="s">
+      <c r="V6" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="W6" s="19">
+      <c r="W6" s="20">
         <v>2</v>
       </c>
-      <c r="X6" s="19" t="s">
+      <c r="X6" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="Y6" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="19" t="s">
+      <c r="Y6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="AA6" s="19">
+      <c r="AA6" s="20">
         <v>52</v>
       </c>
-      <c r="AB6" s="19" t="s">
+      <c r="AB6" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="AC6" s="19">
+      <c r="AC6" s="20">
         <v>85</v>
       </c>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="19"/>
-      <c r="AH6" s="19">
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20">
         <f t="shared" ref="AH6:AH7" si="2">((100-U6)*K6*M6/100+U6*K6*M6*O6/100)</f>
         <v>3.432</v>
       </c>
-      <c r="AI6" s="19">
+      <c r="AI6" s="20">
         <f t="shared" si="1"/>
         <v>3.432</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="1" spans="1:35">
-      <c r="A7" s="18">
+    <row r="7" s="14" customFormat="1" spans="1:37">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>862</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>863</v>
-      </c>
-      <c r="D7" s="19" t="b">
+      <c r="B7" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="D7" s="20" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19">
+      <c r="G7" s="20"/>
+      <c r="H7" s="20">
         <v>9</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="20"/>
+      <c r="J7" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <v>1.1</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="20">
         <v>2.7</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="20">
         <v>2</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="20">
         <v>14</v>
       </c>
-      <c r="R7" s="19" t="s">
+      <c r="R7" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="S7" s="19">
+      <c r="S7" s="20">
         <v>2</v>
       </c>
-      <c r="T7" s="19" t="s">
+      <c r="T7" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="U7" s="19">
+      <c r="U7" s="20">
         <v>15</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="V7" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="W7" s="19">
+      <c r="W7" s="20">
         <v>8</v>
       </c>
-      <c r="X7" s="19" t="s">
+      <c r="X7" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="Y7" s="19">
+      <c r="Y7" s="20">
         <v>2</v>
       </c>
-      <c r="Z7" s="19" t="s">
+      <c r="Z7" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="AA7" s="19">
+      <c r="AA7" s="20">
         <v>42</v>
       </c>
-      <c r="AB7" s="19" t="s">
+      <c r="AB7" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="AC7" s="19">
+      <c r="AC7" s="20">
         <v>70</v>
       </c>
-      <c r="AD7" s="18"/>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="19" t="s">
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="AG7" s="19">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="19">
+      <c r="AG7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="20">
         <f t="shared" si="2"/>
         <v>3.4155</v>
       </c>
-      <c r="AI7" s="19">
+      <c r="AI7" s="20">
         <f t="shared" si="1"/>
         <v>3.4155</v>
       </c>
@@ -17431,285 +18121,6 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="22.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="26.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="12.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="4.57142857142857" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B1" t="s">
-        <v>864</v>
-      </c>
-      <c r="C1" t="s">
-        <v>865</v>
-      </c>
-      <c r="D1" t="s">
-        <v>866</v>
-      </c>
-      <c r="E1" t="s">
-        <v>867</v>
-      </c>
-      <c r="F1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <f t="shared" ref="F2:F12" si="0">E2/$G$2*100</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <f>SUM(E2:E12)</f>
-        <v>578</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4">
-        <v>120</v>
-      </c>
-      <c r="F5" s="5">
-        <f t="shared" si="0"/>
-        <v>20.7612456747405</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>60</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>10.3806228373702</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" s="9">
-        <v>8</v>
-      </c>
-      <c r="E7" s="9">
-        <v>30</v>
-      </c>
-      <c r="F7" s="10">
-        <f t="shared" si="0"/>
-        <v>5.19031141868512</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4">
-        <f>E10*5</f>
-        <v>200</v>
-      </c>
-      <c r="F8" s="5">
-        <f t="shared" si="0"/>
-        <v>34.6020761245675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" t="s">
-        <v>325</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <f>E8/2</f>
-        <v>100</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="0"/>
-        <v>17.3010380622837</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <f>E12*5</f>
-        <v>40</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" si="0"/>
-        <v>6.9204152249135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>270</v>
-      </c>
-      <c r="C11" t="s">
-        <v>336</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <f>E9/5</f>
-        <v>20</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="0"/>
-        <v>3.46020761245675</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11">
-        <v>8</v>
-      </c>
-      <c r="F12" s="12">
-        <f t="shared" si="0"/>
-        <v>1.3840830449827</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
